--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1171"/>
+  <dimension ref="A1:F1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -43849,6 +43849,43 @@
       <c r="F1171" t="inlineStr">
         <is>
           <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaLive enables frame-accurate pipeline locking for streams without timecode</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/medialive-pipeline-locking/</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental MediaLive introduces Video Aligned Locking for frame-accurate synchronization without timecode, simplifying digital streaming workflows.
+2. Outcome (impact):
+Eliminates the need for specialized hardware and complex external workflows, enabling seamless frame-accurate input switching across various outputs.
+3. Where to use (use case):
+Ideal for digital streaming workflows where timecode is unavailable or difficult to manage, such as live sports, news, and event streaming.</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaLive</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -43914,7 +43951,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12 07:49:06</t>
+          <t>2026-09-13 08:10:24</t>
         </is>
       </c>
     </row>
@@ -43925,7 +43962,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -43935,7 +43972,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3042</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -43945,7 +43982,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>993</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -43955,7 +43992,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000216</v>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="9">
@@ -43965,7 +44002,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000282</v>
+        <v>3.3e-05</v>
       </c>
     </row>
     <row r="10">
@@ -43975,7 +44012,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000498</v>
+        <v>5.3e-05</v>
       </c>
     </row>
     <row r="11">
@@ -43985,7 +44022,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07252</v>
+        <v>0.072573</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1172"/>
+  <dimension ref="A1:F1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -43884,6 +43884,267 @@
         </is>
       </c>
       <c r="F1172" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Qwen3.6-35B-A3B-NVFP4 and Wan2.1-T2V-1.3B-Diffusers models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/qwen3.6-35b-a3b-nvfp4-wan2.1-t2v-1.3B-diffusers-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 17:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS now offers Qwen3.6-35B-A3B-NVFP4 for agentic coding and Wan2.1-T2V-1.3B-Diffusers for text-to-video generation on Amazon SageMaker JumpStart.
+2. Outcome (impact):
+   AWS customers can leverage advanced AI models for specialized tasks like long-context reasoning and lightweight video generation, enhancing their AI capabilities.
+3. Where to use (use case):
+   Ideal for developers and enterprises needing sophisticated AI solutions for coding assistance and video content creation.</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Ministral-3-3B-Instruct-2512 and Ministral-3-8B-Instruct-2512 models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/ministral-3-3b-instruct-2512-ministral-3-8B-Instruct-2512-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 17:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Mistral AI's Ministral-3 models are now available on Amazon SageMaker JumpStart, offering compact, vision-capable language models for edge deployment.
+2. Outcome (impact):  
+AWS customers can now deploy high-performance, scalable AI solutions with specialized capabilities for edge and resource-constrained environments.
+3. Where to use (use case):  
+Ideal for ultra-lightweight edge deployment, multilingual instruction following, and vision analysis in various enterprise AI applications.</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>Gemma-4-31B-it-assistant and Gemma-4-31B-IT-NVFP4 models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/gemma-4-31b-it-assistant-gemma-4-31b-it-nvfp4-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 17:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Google DeepMind's Gemma-4-31B-it-assistant and NVIDIA's Gemma-4-31B-IT-NVFP4 models are now available on AWS SageMaker JumpStart, offering scalable AI solutions for enterprise workloads.
+2. Outcome (impact):  
+These models provide high-performance, scalable AI solutions, with the it-assistant variant excelling in multimodal reasoning and the NVFP4 variant offering significant memory savings and faster inference.
+3. Where to use (use case):  
+Ideal for enterprise AI challenges such as multimodal reasoning, coding, agentic workflows, and cost-efficient, high-throughput production deployments.</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>granite-speech-4.1-2b, kanana-2-30b-a3b-instruct, and OpenFold3 models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/granite-speech-4.1-2b-edge-kanana-2-30b-a3b-instruct-openfold3-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has introduced three new models on SageMaker JumpStart: granite-speech-4.1-2b for multilingual ASR, kanana-2-30b-a3b-instruct for bilingual AI workflows, and OpenFold3 for biomolecular structure prediction.
+2. Outcome (impact):  
+These models enhance AWS's AI capabilities, enabling businesses to deploy specialized AI solutions for multilingual speech processing, bilingual AI agentic tasks, and biomolecular research.
+3. Where to use (use case):  
+- granite-speech-4.1-2b: For applications requiring multilingual speech recognition and translation in enterprise voice workflows.
+- kanana-2-30b-a3b-instruct: For bilingual AI agentic tasks, such as customer service chatbots and AI assistants.
+- OpenFold3: For research and development in biomolecular structure prediction in pharmaceuticals and biotechnology.</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>AWS Glue zero-ETL adds target table property ownership and conflict detection</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/glue-zero-etl-ownership-conflicts/</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AWS Glue zero-ETL now detects table property conflicts and tracks ownership, ensuring data lands exactly where intended.
+2. Outcome (impact)
+   Provides predictable control over data integration, preventing conflicts and ensuring data pipelines remain isolated and accurate.
+3. Where to use (use case)
+   Ideal for data teams managing multiple zero-ETL integrations, ensuring source tables are correctly targeted without conflicts.</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging now supports Dynamic Flows in WhatsApp</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-end-user-messaging-whatsapp-dynamic-flows</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS End User Messaging now enables dynamic WhatsApp flows, allowing businesses to create rich, interactive experiences directly within WhatsApp.
+2. Outcome (impact):
+Businesses can enhance customer engagement by providing seamless, interactive experiences without directing users to external websites or forms.
+3. Where to use (use case):
+Use dynamic WhatsApp flows for appointment booking, lead generation, sign-ups, surveys, and transactions, improving user experience and efficiency.</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging strengthens SMS deliverability with automatic failover</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-end-user-messaging-improves-deliverability</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS End User Messaging now offers automatic failover in phone pools to enhance SMS deliverability.
+2. Outcome (impact):  
+Improves SMS delivery reliability by automatically switching to the next best-performing number in the pool during disruptions.
+3. Where to use (use case):  
+Ideal for critical messaging programs such as delivery notifications, one-time passcodes, and reminders.</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -43951,7 +44212,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13 08:10:24</t>
+          <t>2026-09-15 08:32:36</t>
         </is>
       </c>
     </row>
@@ -43962,7 +44223,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -43972,7 +44233,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="7">
@@ -43982,7 +44243,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8">
@@ -43992,7 +44253,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2e-05</v>
+        <v>0.000228</v>
       </c>
     </row>
     <row r="9">
@@ -44002,7 +44263,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3e-05</v>
+        <v>0.000272</v>
       </c>
     </row>
     <row r="10">
@@ -44012,7 +44273,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.3e-05</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="11">
@@ -44022,7 +44283,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.072573</v>
+        <v>0.073073</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1179"/>
+  <dimension ref="A1:F1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -44147,6 +44147,340 @@
       <c r="F1179" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>Monitor cost anomalies directly in Billing and Cost Management Dashboards with the new Detected Anomalies widget</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/monitor-detected-anomalies-using-dashboards</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Billing and Cost Management now includes a Detected Anomalies widget to monitor cost anomalies directly in dashboards, providing immediate insights into cost impacts and root causes.
+2. Outcome (impact):
+Finance teams and cloud administrators can efficiently monitor and investigate cost anomalies within their existing workflows, ensuring better cost management and quicker response to potential issues.
+3. Where to use (use case):
+Ideal for finance teams and cloud administrators who need to keep track of unexpected cost spikes and understand their causes, ensuring optimized cloud spending and budget adherence.</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Billing and Cost Management (BCM)</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect announces flat-rate pricing for dedicated connections</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-direct-connect-announces-flat-rate-pricing/</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Direct Connect introduces flat-rate pricing for 10G and 100G dedicated connections, offering predictable costs for large, sustained data transfer.
+2. Outcome (Impact):
+This pricing model simplifies budgeting for enterprises with large data transfer needs, eliminating variable data transfer charges and providing cost predictability.
+3. Where to Use (Use Case):
+Ideal for enterprises and organizations with consistent, high-volume data transfer requirements, such as large-scale data migrations, continuous data synchronization, and high-throughput applications.</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>AWS Billing Conductor now supports custom rates and usage tier pricing configurations</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/AWS-Billing-Conductor-custom-rates-usage-tier</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 18:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Billing Conductor now allows users to set custom rates and usage tiers for AWS services, simplifying the modeling of commercial agreements.
+2. Outcome (impact):
+This update provides precise control over billing configurations, enabling users to directly reflect negotiated pricing in pro forma billing data without needing to calculate markups or markdowns.
+3. Where to use (use case):
+Ideal for customers and partners who need to model commercial agreements with subsidiaries, affiliates, or end customers, ensuring accurate and customized billing data.</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>AWS Billing Conductor</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI now supports instance preference lists for training and processing jobs</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-sagemaker-training-processing-instance-pref-lists/</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon SageMaker now supports instance preference lists for training and processing jobs, allowing users to specify multiple instance types to improve job start times during high-demand periods.
+2. Outcome (impact):  
+   This feature reduces wait times and unpredictability for AI workloads by automatically selecting the first available instance type from a user-defined list, simplifying job management and improving efficiency.
+3. Where to use (use case):  
+   Ideal for AI training, fine-tuning, and data processing jobs that can run on multiple instance types, particularly during peak periods when specific instance types are in high demand.</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Analyze your CloudTrail events using natural language in Amazon Q Console</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/cloudtrail-amazon-q-console/</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 16:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS CloudTrail now integrates with Amazon Q Console, enabling natural language queries to analyze CloudTrail events for security and operational insights.
+2. Outcome (impact):  
+   Streamlines security investigations and operational troubleshooting by allowing users to query CloudTrail events using natural language, reducing the need for manual log parsing and query writing.
+3. Where to use (use case):  
+   Ideal for security teams investigating incidents, compliance officers auditing configurations, and operational teams troubleshooting issues without deep log analysis expertise.</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Amazon Q Console</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now enables agents to bid on preferred shifts</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-customer-shift-bidding/</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now allows agents to bid on preferred shifts, enhancing control over their schedules and improving scheduling efficiency.
+2. Outcome (Impact):
+   This feature improves agent satisfaction by giving them more control over their schedules and reduces the time schedulers spend on manual assignments.
+3. Where to Use (Use Case):
+   Ideal for contact centers and customer service operations that require flexible and efficient scheduling of agents.</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>AWS Glue zero-ETL now captures archived Salesforce records</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/glue-zero-etl-archived-salesforce/</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue zero-ETL now captures archived Salesforce records, ensuring complete data visibility for analytics.
+2. Outcome (impact):
+Ensures that archived Salesforce data is fully integrated and available for analytics, maintaining data consistency without manual intervention.
+3. Where to use (use case):
+Ideal for organizations requiring comprehensive data analytics on Salesforce data, including archived records like Events, Tasks, and Activities.</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>AWS improves regional resiliency for root user sign-in</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/root-user-regional-resiliency/</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 19:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AWS has enhanced regional resiliency for root user sign-ins by distributing traffic across three US Regions, reducing dependency on a single region.
+2. Outcome (impact)
+   This improvement increases the resiliency of root user sign-ins during service disruptions and automatically routes sign-in requests without requiring user intervention.
+3. Where to use (use case)
+   Ideal for organizations that require high availability and reliability for their root user sign-ins, ensuring uninterrupted access even during regional outages.</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>AWS Identity and Access Management (IAM)</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports ODBC connections for Microsoft Power BI and other analytics tools</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sagemaker-unified-studio-odbc-power-bi/</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker Unified Studio now supports ODBC connections for Microsoft Power BI and other analytics tools, enabling direct access to governed data.
+2. Outcome (impact):  
+Data users can now connect Power BI and other ODBC-compatible tools directly to governed data in SageMaker projects, enhancing workflow efficiency and data analysis capabilities.
+3. Where to use (use case):  
+Ideal for data analysts who use Power BI and need to work with governed data within SageMaker Unified Studio projects.</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: Analytics</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -44212,7 +44546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 08:32:36</t>
+          <t>2026-09-16 08:26:52</t>
         </is>
       </c>
     </row>
@@ -44223,7 +44557,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -44233,7 +44567,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3218</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="7">
@@ -44243,7 +44577,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>956</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="8">
@@ -44253,7 +44587,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000228</v>
+        <v>0.000239</v>
       </c>
     </row>
     <row r="9">
@@ -44263,7 +44597,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000272</v>
+        <v>0.000321</v>
       </c>
     </row>
     <row r="10">
@@ -44273,7 +44607,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0005</v>
+        <v>0.00056</v>
       </c>
     </row>
     <row r="11">
@@ -44283,7 +44617,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.073073</v>
+        <v>0.073633</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1188"/>
+  <dimension ref="A1:F1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -44481,6 +44481,489 @@
       <c r="F1188" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>Amazon Corretto 27 is now generally available</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-corretto-27-generally-available/</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 00:00:31 GMT</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Corretto 27, a new feature release, is now available with enhanced performance, security, and memory efficiency. It includes G1 as the default garbage collector, post-quantum TLS support, and compact object headers.
+2. Outcome (impact):
+- Improved application performance and predictability with G1 garbage collector.
+- Enhanced security against future quantum computing threats.
+- Better memory efficiency with compact object headers.
+- Protection of sensitive data during diagnostics.
+3. Where to use (use case):
+- Java applications requiring consistent performance and security.
+- Applications needing to future-proof against quantum computing.
+- Memory-intensive applications benefiting from reduced object size.</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Amazon Corretto</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI now supports serverless model customization for NVIDIA Nemotron 3.5 Lightning</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-sagemaker-ft-nemotron-3-5-lightning/</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 22:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker now supports serverless customization of the NVIDIA Nemotron 3.5 Lightning model using SFT, DPO, and RFT.
+2. Outcome (impact):
+Reduces costs and latency by enabling domain-specific model fine-tuning without managing infrastructure.
+3. Where to use (use case):
+Adapting large language models to specific business needs and workflows, such as improving task accuracy or aligning model outputs with organizational standards.</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>AWS Client VPN is now supporting MacOS 27 Golden Gate</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-client-vpn-macos-golden-gate/</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 17:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Client VPN now supports MacOS 27 Golden Gate with client versions 6.0+, enabling secure remote access to AWS networks.
+2. Outcome (impact):  
+This update enhances remote connectivity for MacOS users, ensuring they can securely access AWS resources with the latest MacOS version.
+3. Where to use (use case):  
+Ideal for remote employees needing secure access to AWS or on-premises networks using the latest MacOS Golden Gate.</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>AWS Client VPN</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>New AWS experience helps builders get started and ship faster</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/New-AWS-Builder-Experience</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 17:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces a simplified experience for developers to quickly start projects with sensible defaults and streamlined setup, using existing credentials and offering free credits.
+2. Outcome (impact):
+   Developers can start implementing their ideas faster, reduce initial setup effort, and manage project costs more effectively with automated configurations and spend limits.
+3. Where to use (use case):
+   Ideal for startups, small teams, and individual developers looking to quickly prototype and deploy applications on AWS without extensive initial configuration.</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>AWS Management Console</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces adds support for NVIDIA Blackwell GPU instances</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-workspaces-nvidia-blackwell-gpu-instances/</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces now supports new Graphics G7 bundles with advanced NVIDIA RTX PRO 4500 Blackwell GPUs, enhancing performance for graphics-intensive tasks.
+2. Outcome (Impact):
+Users can achieve up to 2.1x better performance for demanding applications like CAD, 3D rendering, and AI-assisted design, with improved fidelity and frame rates.
+3. Where to Use (Use Case):
+Ideal for professionals in CAD/CAM, 3D rendering, scientific visualization, video editing, and AI-assisted design workflows.</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer custom metrics now supports tag-based access control</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/connect-customer-custom-metrics-tag/</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect now allows tag-based access control for custom metrics, enabling better governance and security over who can view, create, or modify metrics.
+2. Outcome (impact):
+   This update helps organizations manage custom metrics more effectively by preventing unauthorized changes and ensuring that only authorized teams can access or modify specific metrics.
+3. Where to use (use case):
+   Ideal for organizations with multiple teams using Amazon Connect, ensuring that each team can manage their own metrics without interfering with others.</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer can now import evaluation form PDFs using AI</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-customer-import-evaluation-form-PDF/</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now allows managers to import evaluation form PDFs from third-party applications and automatically recreate them using AI, simplifying the migration of existing quality programs.
+2. Outcome (impact):
+   This feature reduces the time and effort required to set up evaluation forms in Amazon Connect, minimizing manual edits and ensuring a smoother transition of quality management processes.
+3. Where to use (use case):
+   Ideal for quality assurance teams and managers who need to migrate existing evaluation forms from other quality management systems into Amazon Connect without manually recreating each form.</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor Monetization Functions adds ad response hooks</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-elemental-mediatailor-functions-ad-response-hooks</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elemental MediaTailor introduces new lifecycle hooks for monetization functions, enabling advanced ad management and insertion.
+2. Outcome (impact):  
+Enhanced ad personalization and control, allowing for dynamic ad sourcing and policy enforcement, improving ad relevance and compliance.
+3. Where to use (use case):  
+Ideal for video streaming services needing to manage ad content dynamically, ensuring ads meet brand policies and fill ad slots effectively.</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Amazon ECS extends Amazon S3 Files support to the Amazon EC2 compute type</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ecs-s3-files-ec2/</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 16:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now supports Amazon S3 Files for EC2 tasks, enabling seamless access to S3 data as a shared file system.
+2. Outcome (impact):
+Customers can run file-based applications and data processing workloads on S3 data without code changes, enhancing efficiency and reducing data duplication.
+3. Where to use (use case):
+Ideal for applications requiring direct, low-latency access to S3 data, such as AI agents, data processing, and file-based workloads on EC2 instances.</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now lets you create, manage, and search custom metrics through APIs</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/connect-customer-custom-metrics-apis/</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers API-driven management of custom metrics, ensuring consistency and reliability across various business environments.
+2. Outcome (impact):
+Ensures metric definitions remain consistent and accurate as businesses scale, improving decision-making based on reliable data.
+3. Where to use (use case):
+Ideal for customer experience teams needing to track specific, business-unique metrics across multiple instances, such as monitoring self-service abandonment rates.</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>AWS STS simplifies session token size limits and adds session token size monitoring</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-sts/</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 22:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS STS now enforces a unified 4,096-byte limit on session tokens and provides monitoring for token size.
+2. Outcome (impact):  
+This change simplifies token management and offers better flexibility for combining session policies and tags, while also providing detailed monitoring.
+3. Where to use (use case):  
+Ideal for applications requiring larger session tokens to handle more complex policies and tags, ensuring they can manage larger token sizes effectively.</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>AWS Security Token Service (STS)</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>AWS Step Functions adds new AWS service integrations automatically, starting with AWS Lambda MicroVMs</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-step-functions-integrations/</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 18:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Step Functions now automatically integrates new AWS services, starting with Lambda MicroVMs, enabling faster orchestration of the latest capabilities.
+2. Outcome (impact):
+Users can now orchestrate the latest AWS services without waiting for manual updates, streamlining workflows and improving efficiency.
+3. Where to use (use case):
+Ideal for building distributed applications that require secure, isolated execution environments and need to integrate multiple AWS services seamlessly.</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>AWS Step Functions</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>AWS PCS now supports custom GRES, hardware topology, and MIG</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-pcs-gres-hardware-topology-mig/</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>1. Short Summary: AWS PCS now supports custom GRES, hardware topology, and MIG for better HPC and ML task placement.
+2. Outcome (impact): Improved control over cluster hardware scheduling, enabling optimized job placement and resource utilization for HPC and ML workloads.
+3. Where to use (use case): Ideal for high-performance computing (HPC) and machine learning (ML) tasks requiring fine-tuned resource management and scheduling.</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service (AWS PCS)</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -44546,7 +45029,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16 08:26:52</t>
+          <t>2026-09-17 08:32:31</t>
         </is>
       </c>
     </row>
@@ -44557,7 +45040,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -44567,7 +45050,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3366</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="7">
@@ -44577,7 +45060,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1132</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="8">
@@ -44587,7 +45070,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000239</v>
+        <v>0.000366</v>
       </c>
     </row>
     <row r="9">
@@ -44597,7 +45080,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000321</v>
+        <v>0.000456</v>
       </c>
     </row>
     <row r="10">
@@ -44607,7 +45090,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00056</v>
+        <v>0.000822</v>
       </c>
     </row>
     <row r="11">
@@ -44617,7 +45100,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.073633</v>
+        <v>0.07445499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1201"/>
+  <dimension ref="A1:F1212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -44964,6 +44964,413 @@
       <c r="F1201" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family now supports source IP preservation for SFTP servers behind a Network Load Balancer (NLB)</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/transfer-family-sftp-source-ip-nlb/</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transfer Family now supports source IP preservation for SFTP servers behind an NLB using Proxy Protocol v2.
+2. Outcome (impact):  
+This update allows for better visibility and control over client IPs for auditing, access controls, and compliance.
+3. Where to use (use case):  
+Ideal for environments requiring IP-based access controls and auditing, such as financial services, healthcare, and regulated industries.</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports IAM session policies</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/omics-iam-session-policy/</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 18:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now supports IAM session policies, allowing dynamic permission restrictions for individual runs without multiple IAM roles.
+2. Outcome (impact):
+This feature enables more granular control over permissions for each run, enhancing security and simplifying IAM management for multi-tenant applications.
+3. Where to use (use case):
+Ideal for multi-tenant applications where different runs need isolated access to specific resources, such as Amazon S3 buckets, without creating separate IAM roles for each tenant.</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>AWS Batch now supports bulk job cancellation and termination</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-batch-bulk-cancellation/</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 17:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+AWS Batch now allows bulk cancellation and termination of up to 50 jobs with a single API call, simplifying large-scale batch workload management.
+2. Outcome (impact)
+Reduces operational complexity and time spent managing large-scale batch workloads by enabling efficient bulk job actions and providing better job lifecycle tracking.
+3. Where to use (use case)
+Ideal for managing large batch processing tasks in environments where quick and efficient job management is critical, such as data processing pipelines, scientific simulations, and large-scale data analysis.</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>AWS Batch</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>Introducing Amazon EC2 T8i instances</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-t8i-instances-ga/</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched new low-cost burstable T8i instances with improved performance and price efficiency, powered by custom Intel Xeon processors and AWS Nitro cards.
+2. Outcome (impact):
+T8i instances offer up to 30% better price performance and up to 70% higher compute performance compared to T3 instances, reducing total cost of ownership (TCO) for existing users and providing a cost-effective entry point for new users.
+3. Where to use (use case):
+Ideal for workloads with low to moderate CPU utilization such as data processing, login gateways, small databases, batch processing, event-driven functions, CI/CD pipelines, microservices, and low traffic websites.</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>AWS Elastic Beanstalk introduces Cluster Mode to run multiple applications on shared infrastructure</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/elastic-beanstalk-cluster-mode/</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Elastic Beanstalk introduces Cluster Mode, enabling multiple applications to run on shared infrastructure, reducing costs and simplifying management.
+2. Outcome (impact):
+   This new deployment mode allows for cost savings by pooling infrastructure, supports event-driven autoscaling, and integrates with observability tools and AWS services.
+3. Where to use (use case):
+   Ideal for microservices architectures and environments with multiple small to medium-sized applications that can benefit from shared resources.</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Elastic Beanstalk</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>Amazon S3 Express One Zone is now available in 7 additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/s3-express-one-zone-7-regions/</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Express One Zone is now available in 7 new regions, offering high-performance, single-digit millisecond data access for latency-sensitive applications.
+2. Outcome (impact):
+Enhanced performance and cost efficiency for machine learning, interactive analytics, and key-value caching applications across 15 AWS regions.
+3. Where to use (use case):
+Ideal for machine learning training, interactive analytics, and key-value caching in AI search engines requiring fast data access.</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Amazon S3 Express One Zone</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>AWS Builder Center now available as mobile app on iOS and Android</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-builder-center-now-available-as-mobile-app/</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 07:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Builder Center is now accessible via a mobile app on iOS and Android, offering global builders community resources, courses, and events on-the-go.
+2. Outcome (impact):
+This mobile app enhances accessibility for builders, allowing them to engage with the AWS community, access learning resources, and participate in events from anywhere, improving their learning and engagement experience.
+3. Where to use (use case):
+Ideal for developers and tech enthusiasts who need to stay updated with the latest AWS resources, participate in community events, and manage their learning and feedback on AWS products while on the move.</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>AWS Builder Center</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>Amazon Quick now generates individual sheets and builds analyses from an image</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/generate-sheet-and-generate-analysis-from-an-image/</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 02:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick now allows users to generate individual sheets and entire analyses from natural language descriptions and dashboard images.
+2. Outcome (impact):
+   This update significantly speeds up dashboard creation and analysis generation, reducing manual effort and enabling faster data insights.
+3. Where to use (use case):
+   Ideal for data analysts and business users who need to quickly create and modify dashboards and analyses without extensive manual setup.</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Amazon QuickSight</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>Amazon ECS deployment observability for Amazon ECS Managed Daemons in AWS Management Console</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ecs-daemon-deployment-console/</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 22:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon ECS now offers a unified deployment view for Managed Daemons, simplifying monitoring and troubleshooting of deployment progress and failures.
+2. Outcome (impact):  
+Faster resolution of deployment issues and better visibility into the deployment lifecycle, reducing the need to gather information from multiple sources.
+3. Where to use (use case):  
+Ideal for DevOps teams managing containerized applications on Amazon ECS, ensuring smooth and efficient deployment processes.</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces (for Apache Cassandra) is now generally available in 11 additional Regions</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-keyspaces/</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon Keyspaces (for Apache Cassandra) is now available in 11 new regions, enabling lower latency and data residency compliance.
+2. Outcome (impact)
+Customers can now build Cassandra-compatible applications with reduced latency and better data residency compliance in 11 additional regions.
+3. Where to use (use case)
+Use Amazon Keyspaces for building scalable, high-performance, and managed Cassandra-compatible applications that require low latency and data residency within specific regions.</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>Amazon Connect Talent is now generally available</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-talent/</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 12:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Talent is now available, offering an AI-powered hiring solution to accelerate candidate selection with structured interviews and assessments.
+2. Outcome (impact):
+This service accelerates hiring processes, enhances consistency in candidate evaluation, and allows recruiters to focus on strategic decisions by leveraging AI.
+3. Where to use (use case):
+Ideal for talent acquisition teams in large organizations looking to scale their hiring processes efficiently and objectively.</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Amazon Connect Talent</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -45029,7 +45436,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 08:32:31</t>
+          <t>2026-09-18 08:07:12</t>
         </is>
       </c>
     </row>
@@ -45040,7 +45447,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -45050,7 +45457,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5157</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="7">
@@ -45060,7 +45467,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1604</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="8">
@@ -45070,7 +45477,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000366</v>
+        <v>0.000283</v>
       </c>
     </row>
     <row r="9">
@@ -45080,7 +45487,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000456</v>
+        <v>0.000391</v>
       </c>
     </row>
     <row r="10">
@@ -45090,7 +45497,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000822</v>
+        <v>0.000674</v>
       </c>
     </row>
     <row r="11">
@@ -45100,7 +45507,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07445499999999999</v>
+        <v>0.075129</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1212"/>
+  <dimension ref="A1:F1221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -45371,6 +45371,340 @@
       <c r="F1212" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>AWS Continuum now supports credential testing and accessible domain suggestions</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-security-agent/</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 18:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Continuum now offers credential testing and accessible domain suggestions to enhance penetration testing accuracy and efficiency.
+2. Outcome (impact):
+This update reduces misconfigurations and wasted test cycles by allowing teams to validate credentials and identify in-scope URLs before running a full penetration test.
+3. Where to use (use case):
+Ideal for developers and security teams to ensure accurate network scope configuration and effective penetration testing of web applications.</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>AWS Continuum</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>Amazon ECS Express Mode now supports AWS Graviton (ARM64) workloads</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ecs-express-mode-arm-architecture/</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 17:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS Express Mode now supports ARM64 architecture, enabling deployment of ARM-based container images on AWS Graviton instances for improved price-performance.
+2. Outcome (impact):
+Users can now deploy ARM64 container images on AWS Graviton instances, achieving up to 40% better price-performance compared to x86-based instances.
+3. Where to use (use case):
+Ideal for deploying cost-optimized, high-performance containerized applications, especially those built natively for ARM architecture.</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>AWS Resilience Hub adds three new capabilities</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/resilience-hub-eks-dependency-policy/</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 16:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Resilience Hub has introduced three new capabilities to enhance workload resilience on AWS, including EKS labels support, dependency insights, and resilience policy sharing.
+2. Outcome (Impact):
+These enhancements improve the accuracy of resilience assessments, accelerate dependency analysis, and enable better organization-wide resilience management.
+3. Where to Use (Use Case):
+Ideal for platform engineering and site reliability teams managing multi-account environments to ensure consistent resilience postures across their AWS workloads.</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>AWS Resilience Hub</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>AWS RTB Fabric now supports configurable Availability Zone affinity</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-rtb-fabric-configurable-availability-zone-affinity/</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS RTB Fabric now allows advertisers to configure Availability Zone affinity for responder gateways, optimizing connection efficiency and latency.
+2. Outcome (impact):  
+This update enables AdTech companies to use their infrastructure more efficiently by balancing latency and capacity utilization, without incurring additional charges.
+3. Where to use (use case):  
+Demand-side platforms (DSPs) and supply-side platforms (SSPs) can use this feature to manage how their bidding systems connect to responder gateways across multiple Availability Zones.</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Service Name: AWS RTB Fabric  
+Category: Networking</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>Kimi K3 by Moonshot AI is now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/moonshot-ai-kimi-k3-on-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 15:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Kimi K3 by Moonshot AI, now available on Amazon Bedrock, is a powerful open model with 2.8 trillion parameters, designed for coding and knowledge work.
+2. Outcome (impact):
+   Enhances coding efficiency and multi-document analysis with improved scaling efficiency and reduced latency through explicit prompt caching.
+3. Where to use (use case):
+   Ideal for long-running coding sessions, multi-document analysis, and extended agent workflows.</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>Amazon SNS now supports message payloads up to 1 MiB</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-sns-1mib-support</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SNS now supports message payloads up to 1 MiB, allowing larger messages to be published to SNS topics.
+2. Outcome (Impact):
+   This update enables users to handle larger data payloads within a single message, facilitating more efficient data exchange for applications like IoT and generative AI.
+3. Where to Use (Use Case):
+   Ideal for microservices, distributed systems, and serverless applications that require sending larger data payloads, such as application integration, IoT data transmission, and generative AI workflows.</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Amazon SNS</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>The new AgentCore Runtime is now available in Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/new-agentcore-runtime-generally-available</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 13:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the next-generation AgentCore Runtime in Amazon Bedrock AgentCore, featuring elastic memory management and consistent cold start times.
+2. Outcome (impact):
+Users will benefit from lower costs due to efficient memory usage and faster session starts, improving overall performance and cost-effectiveness.
+3. Where to use (use case):
+Ideal for applications requiring scalable, serverless compute resources with predictable costs and quick startup times, such as chatbots, microservices, and serverless applications.</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>AWS PrivateLink announces Tunnel Endpoints to access network segments</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/9/privatelink-tunnel-endpoint/</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS PrivateLink now supports Tunnel Endpoints to securely access network segments across VPCs/accounts using VPC endpoints.
+2. Outcome (impact):
+   This new feature allows for more efficient and secure sharing of network segments with external vendors, reducing the need for individual resource configurations.
+3. Where to use (use case):
+   Ideal for scenarios where secure, private access to a range of network resources is needed, such as sharing a network segment with a vendor or partner.</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>AWS PrivateLink</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>Amazon SES now supports tenant-level deliverability insights</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ses-vdm-tenants/</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SES now offers tenant-level deliverability insights in VDM, enabling isolated monitoring and management of email sending across different tenants.
+2. Outcome (impact):  
+This update allows email senders to identify and resolve deliverability issues specific to individual tenants without affecting other tenants, improving overall email campaign performance.
+3. Where to use (use case):  
+Ideal for multi-tenant SaaS applications, businesses managing email campaigns for different clients, or organizations needing to isolate email sending for various business units or applications.</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -45436,7 +45770,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:07:12</t>
+          <t>2026-09-19 07:56:25</t>
         </is>
       </c>
     </row>
@@ -45447,7 +45781,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -45457,7 +45791,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3989</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="7">
@@ -45467,7 +45801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1377</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="8">
@@ -45477,7 +45811,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000283</v>
+        <v>0.000255</v>
       </c>
     </row>
     <row r="9">
@@ -45487,7 +45821,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000391</v>
+        <v>0.000319</v>
       </c>
     </row>
     <row r="10">
@@ -45497,7 +45831,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000674</v>
+        <v>0.000574</v>
       </c>
     </row>
     <row r="11">
@@ -45507,7 +45841,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.075129</v>
+        <v>0.07570300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1221"/>
+  <dimension ref="A1:F1222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -45705,6 +45705,43 @@
       <c r="F1221" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X8i instances are now available in the South America (São Paulo) Region</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-x8i-south-america-sao-paulo/</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 22:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EC2 X8i instances, powered by custom Intel Xeon 6 processors, are now available in the South America (São Paulo) region, offering enhanced performance and memory capacity.
+2. Outcome (impact):  
+X8i instances deliver up to 43% higher performance and 1.5x more memory capacity compared to previous generation X2i instances, making them ideal for memory-intensive workloads.
+3. Where to use (use case):  
+Ideal for workloads such as SAP HANA, large databases, data analytics, and Electronic Design Automation (EDA).</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -45770,7 +45807,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19 07:56:25</t>
+          <t>2026-09-21 08:46:29</t>
         </is>
       </c>
     </row>
@@ -45781,7 +45818,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -45791,7 +45828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3590</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7">
@@ -45801,7 +45838,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -45811,7 +45848,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000255</v>
+        <v>2.6e-05</v>
       </c>
     </row>
     <row r="9">
@@ -45821,7 +45858,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000319</v>
+        <v>4.1e-05</v>
       </c>
     </row>
     <row r="10">
@@ -45831,7 +45868,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000574</v>
+        <v>6.7e-05</v>
       </c>
     </row>
     <row r="11">
@@ -45841,7 +45878,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07570300000000001</v>
+        <v>0.07577</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1222"/>
+  <dimension ref="A1:F1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -45740,6 +45740,117 @@
         </is>
       </c>
       <c r="F1222" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>Amazon ECS now provides real-time deployment observability in the AWS Management Console</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ecs-console-deployment-observability/</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 20:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECS now offers real-time deployment observability in the AWS Management Console for Linear, Canary, and Blue/Green deployments.
+2. Outcome (impact):
+   Enhanced deployment monitoring and troubleshooting capabilities, reducing time to diagnose and resolve issues.
+3. Where to use (use case):
+   Ideal for developers and DevOps teams managing containerized applications, ensuring smooth and reliable service deployments.</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>Amazon EVS now in scope for FedRAMP Class C</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-evs-fedramp-class-c/</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 19:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Elastic VMware Service (EVS) is now FedRAMP Class C compliant in all U.S. regions, enhancing security for government workloads.
+2. Outcome (impact):
+This compliance enables government agencies to migrate workloads to AWS more securely, reducing operational risks and meeting regulatory requirements.
+3. Where to use (use case):
+Ideal for government agencies needing to migrate VMware workloads to AWS while ensuring compliance with FedRAMP Moderate baseline.</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Amazon Elastic VMware Service (EVS)</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I7ie instances now available in AWS Israel region</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ec2-i7ie-instances-israel-telaviv-region/</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched I7ie instances in the Israel (Tel Aviv) region, offering high storage I/O performance and enhanced compute capabilities.
+2. Outcome (impact):
+I7ie instances provide up to 40% better compute performance and 20% better price performance, along with significant improvements in storage performance and latency.
+3. Where to use (use case):
+Ideal for large storage I/O intensive workloads, such as data warehousing, big data analytics, and high-performance computing applications.</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -45807,7 +45918,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 08:46:29</t>
+          <t>2026-09-22 08:24:25</t>
         </is>
       </c>
     </row>
@@ -45818,7 +45929,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -45828,7 +45939,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7">
@@ -45838,7 +45949,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
@@ -45848,7 +45959,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6e-05</v>
+        <v>7.8e-05</v>
       </c>
     </row>
     <row r="9">
@@ -45858,7 +45969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1e-05</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="10">
@@ -45868,7 +45979,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.7e-05</v>
+        <v>0.000178</v>
       </c>
     </row>
     <row r="11">
@@ -45878,7 +45989,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07577</v>
+        <v>0.075948</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1225"/>
+  <dimension ref="A1:F1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -45853,6 +45853,413 @@
       <c r="F1225" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Omni: AI-first observability for agents and applications</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-cloudwatch-omni-ai/</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 00:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS launches Amazon CloudWatch Omni, an AI-powered observability tool for monitoring applications and agents across AWS and other clouds, enhancing troubleshooting and operational workflows.
+2. Outcome (impact):
+CloudWatch Omni streamlines observability by integrating telemetry from multiple sources, enabling faster issue resolution and improved application performance through AI-driven insights.
+3. Where to use (use case):
+Ideal for DevOps teams and application developers needing a unified view of their applications' health and performance across various environments, including multi-cloud setups.</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Omni</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>Billing Transfer now supports automatic billing group creation for two-level transfers</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-billing-transfer-supports-automatic-billing-group-creation/</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 20:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Billing Transfer now supports automatic billing group creation for two-level transfers, simplifying the configuration for AWS Distributors.
+2. Outcome (impact):
+   This feature reduces manual effort and ensures immediate availability of pro forma cost data for downstream seller Partners and their end customers.
+3. Where to use (use case):
+   Ideal for AWS Distributors managing billing for downstream seller Partners and their end customers, ensuring seamless billing transfer arrangements.</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>AWS Billing Conductor</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-6 Sol and GPT-6 Luna are now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/openai-gpt-6-sol-luna-on-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 18:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has made GPT-6 Sol and GPT-6 Luna from OpenAI available on Amazon Bedrock, enhancing capabilities for complex tasks and high-volume processing.
+2. Outcome (Impact):
+These models offer improved accuracy and efficiency for software development and high-volume data processing tasks, reducing errors and enhancing productivity.
+3. Where to Use (Use Case):
+Ideal for software development, data analysis, summarization, classification, and routing tasks requiring high accuracy and efficiency.</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>Claude Opus 5.5 is now available on AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-opus-5-5-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS GovCloud (US) now offers Anthropic’s latest model, Claude Opus 5.5, enhancing task efficiency and reporting capabilities for long-running coding and knowledge work.
+2. Outcome (impact):  
+Improved efficiency in long-running coding and knowledge tasks, lower costs, and better reporting, making it a more reliable tool for enterprise use.
+3. Where to use (use case):  
+Ideal for enterprise environments requiring advanced coding assistance, knowledge work, and detailed task reporting.</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>Claude Opus 5.5 is now available on AWS</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-opus-5-5-aws/</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now offers Anthropic’s latest model, Claude Opus 5.5, enhancing task efficiency and reporting for coding and knowledge work.
+2. Outcome (impact):
+Improved task efficiency, lower costs, and better reporting for long-running coding and knowledge tasks, making it a more reliable tool for enterprise use.
+3. Where to use (use case):
+Ideal for enterprise-level coding projects, knowledge work, and tasks requiring detailed reporting and adaptive task management.</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>Amazon EMR introduces Long Term Support with Apache Spark 4.1</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-emr-long-term-support-spark-4-1/</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR introduces Long Term Support (LTS) for Apache Spark 4.1, offering 36 months of support for critical fixes and new features like Apache Iceberg v3 support.
+2. Outcome (impact):
+This release allows users to maintain production Spark workloads on a stable release for an extended period, improving security and stability while enabling new data management capabilities.
+3. Where to use (use case):
+Ideal for data engineering and analytics teams managing large-scale data processing tasks, ensuring long-term stability and leveraging new features like Apache Iceberg.</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver is now generally available on second-generation AWS Outposts racks</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/route-53-resolver-gen2-outposts/</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Route 53 Resolver is now available on second-gen AWS Outposts, offering local DNS resolution to reduce latency and improve reliability.
+2. Outcome (impact):
+Reduces latency for DNS queries, ensures continuous DNS resolution during connectivity interruptions, and eliminates the need for customer-managed compute capacity.
+3. Where to use (use case):
+Ideal for organizations needing local DNS resolution for workloads running on AWS Outposts to minimize latency and maintain service continuity.</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>AWS Security Hub AI Inventory adds Azure self-hosted instance support</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/security-hub-ai-inventory-azure-support/</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Security Hub AI Inventory now supports Azure self-hosted instances, enhancing multi-cloud AI asset visibility and security.
+2. Outcome (impact):  
+Centralized, continuous monitoring and management of AI assets across AWS and Azure, improving security posture and compliance.
+3. Where to use (use case):  
+Ideal for organizations with multi-cloud deployments needing unified visibility and security management of AI assets.</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>Amazon EMR 7.14 is now available</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-emr-7-14-available/</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR 7.14 is now available with enhanced features for EC2, EKS, and Serverless, including faster Apache Iceberg materialized views, Spark Connect endpoints, and increased storage for Spark jobs.
+2. Outcome (impact):
+Improved performance and efficiency in data processing and analytics, enabling faster data refreshes, more secure interactive sessions, and larger data handling capabilities.
+3. Where to use (use case):
+Ideal for data engineering tasks, big data processing, and analytics workloads requiring enhanced performance and security in cloud environments.</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality delivers context-specific rule recommendations in seconds</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/glue-data-quality-rule-recommendations/</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Glue Data Quality now uses generative AI to quickly recommend data quality rules, reducing setup time and ensuring faster data trust.
+2. Outcome (impact):
+   Reduces time to establish data quality checks, accelerates the transition from raw to trusted data, and minimizes manual rule creation.
+3. Where to use (use case):
+   Ideal for onboarding new datasets, establishing baseline checks across large data lakes, and ensuring data quality in data pipelines.</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom now supports the latest CU for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-custom-supports-latest-cu-gdr-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS Custom now supports the latest Cumulative Update for Microsoft SQL Server, including SQL Server 2022 CU26.
+2. Outcome (impact):
+   Users can now benefit from the latest security patches, performance improvements, and new features in Microsoft SQL Server 2022 CU26.
+3. Where to use (use case):
+   Ideal for enterprise applications requiring the latest SQL Server updates for compliance, performance, and new features.</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -45918,7 +46325,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24:25</t>
+          <t>2026-09-23 08:26:35</t>
         </is>
       </c>
     </row>
@@ -45929,7 +46336,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -45939,7 +46346,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1098</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="7">
@@ -45949,7 +46356,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>353</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="8">
@@ -45959,7 +46366,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.8e-05</v>
+        <v>0.000289</v>
       </c>
     </row>
     <row r="9">
@@ -45969,7 +46376,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001</v>
+        <v>0.000387</v>
       </c>
     </row>
     <row r="10">
@@ -45979,7 +46386,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000178</v>
+        <v>0.000676</v>
       </c>
     </row>
     <row r="11">
@@ -45989,7 +46396,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.075948</v>
+        <v>0.076624</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1236"/>
+  <dimension ref="A1:F1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -46260,6 +46260,228 @@
       <c r="F1236" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams announces Service-Managed Partition Keys for simplified data ingestion</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/kinesis/service-managed-partition-keys</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 22:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Kinesis Data Streams now offers service-managed partition keys, simplifying data ingestion for On-Demand streams by automatically distributing records across shards.
+2. Outcome (impact):
+   This feature eliminates the need for customers to specify partition keys, reducing throttling and simplifying scaling, thus lowering the time to production for streaming workloads.
+3. Where to use (use case):
+   Ideal for use cases like log aggregation, metrics collection, and IoT telemetry where record ordering is not required.</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base now supports Salesforce and Zendesk as native data source connectors</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-managed-knowledge-base-salesforce-zendesk-native-data-source-connectors/</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 17:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces native Salesforce and Zendesk data source connectors for Amazon Bedrock Managed Knowledge Base, automating data sync for AI applications.
+2. Outcome (impact):
+Eliminates the need for custom pipelines, ensuring knowledge bases are always up-to-date with minimal manual intervention.
+3. Where to use (use case):
+Ideal for creating customer support bots and internal sales assistants that require access to the latest Salesforce and Zendesk content.</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now provides routing step data in the analytics data lake</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-routing-step-data/</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers routing step data in the analytics data lake, enabling easier insights from routing decisions.
+2. Outcome (impact):
+Customers can analyze routing trends, identify criteria relaxations, and measure routing impact on wait times and agent utilization with minimal setup.
+3. Where to use (use case):
+Optimize contact center operations by analyzing how contacts progress through routing steps and adjusting configurations to improve efficiency.</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>Amazon EMR on EKS now supports IPv6 Amazon EKS clusters</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-emr-eks-ipv6-support</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has enabled Amazon EMR on EKS to support IPv6 clusters, allowing larger address spaces for big data workloads.
+2. Outcome (impact):
+This update allows data teams to scale large Spark and Flink workloads without IPv4 address limitations, enhancing operational efficiency.
+3. Where to use (use case):
+Ideal for data platform and analytics teams running large-scale big data frameworks on Amazon EKS.</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Amazon EMR on EKS</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB global tables with multi-Region strong consistency now supports additional AWS Regions and cross-continent configurations</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/dynamodb-mrsc-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DynamoDB now supports multi-Region strong consistency in five new regions, enhancing global application availability and consistency.
+2. Outcome (impact):
+   Enables highly available, multi-Region applications with zero RPO, suitable for global businesses requiring strict data consistency.
+3. Where to use (use case):
+   Ideal for applications like user profile management, inventory tracking, order state, and entitlement management that need consistent data across regions.</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>DynamoDB</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches agent-to-agent collaboration</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/Amazon-Connect-Customer-A2A</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer now supports agent-to-agent collaboration, enabling specialized AI agents to work together during live interactions to enhance customer service.
+2. Outcome (impact):  
+This feature improves efficiency and effectiveness in resolving customer issues by allowing AI agents to collaborate and delegate tasks, leading to faster and more accurate resolutions.
+3. Where to use (use case):  
+Use this in customer service scenarios where complex issues require specialized expertise, such as fraud detection and dispute resolution in banking.</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -46325,7 +46547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23 08:26:35</t>
+          <t>2026-09-24 08:18:38</t>
         </is>
       </c>
     </row>
@@ -46336,7 +46558,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -46346,7 +46568,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="7">
@@ -46356,7 +46578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1363</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -46366,7 +46588,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000289</v>
+        <v>0.000155</v>
       </c>
     </row>
     <row r="9">
@@ -46376,7 +46598,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000387</v>
+        <v>0.000199</v>
       </c>
     </row>
     <row r="10">
@@ -46386,7 +46608,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000676</v>
+        <v>0.000354</v>
       </c>
     </row>
     <row r="11">
@@ -46396,7 +46618,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.076624</v>
+        <v>0.076978</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1242"/>
+  <dimension ref="A1:F1254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -46482,6 +46482,450 @@
       <c r="F1242" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>AWS Billing and Cost Management now provides billing context for your account through a new API</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-billing-and-cost-management-billing-context-api/</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 00:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Billing and Cost Management now offers the ListBillingViewSegments API to provide billing context for your account, detailing account hierarchy and billing settings over specified time periods.
+2. Outcome (impact):
+This API helps users better understand their billing relationships and rate settings, improving financial oversight and management of AWS costs.
+3. Where to use (use case):
+Use this API to analyze billing context for auditing, compliance, and cost management, especially in complex organizational structures with multiple accounts and changing billing relationships.</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>AWS Billing and Cost Management</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>Amazon EventBridge relaunches event buses for enterprise scale</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/eventbridge-relaunches-custom-event-buses/</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EventBridge has relaunched its Custom event buses to support enterprise-scale event-driven applications with enhanced features for scalability, ordering, and retention.
+2. Outcome (impact):
+The new Custom event bus allows teams to build decoupled applications that can scale with the organization, ensuring strict event ordering, support for advanced transformations, and built-in retention.
+3. Where to use (use case):
+Use the enhanced Custom event bus for building scalable, event-driven architectures that require decoupling of teams, strict event ordering, and integration with multiple AWS services.</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Amazon EventBridge</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>AWS Lambda durable functions are now available in AWS European Sovereign Cloud region</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/durablefunctions-european-sovereign-cloud/</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 18:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda durable functions are now available in the AWS European Sovereign Cloud, enabling developers to build reliable multi-step applications and AI workflows with enhanced reliability and compliance.
+2. Outcome (impact):
+   This update allows developers to create robust, fault-tolerant applications and workflows that can checkpoint progress, recover from failures, and pause executions without incurring compute charges, all while meeting stringent compliance and security requirements.
+3. Where to use (use case):
+   Use cases include order workflows, user onboarding processes, and AI-assisted tasks that require reliable, multi-step operations within a secure and compliant environment.</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL announces Extended Support minor versions 5.7.44-rds.20260902 and 8.0.46-rds.20260908</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-mysql-extended-support-minor-5744-8046-rds/</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for MySQL introduces Extended Support minor versions 5.7.44 and 8.0.46, offering up to three extra years of critical fixes beyond standard support.
+2. Outcome (impact):
+Users gain extended security and bug fixes, allowing more time to upgrade to newer major versions without immediate pressure.
+3. Where to use (use case):
+Ideal for businesses needing extended security patches and stability for critical applications while planning major version upgrades.</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL now supports PostgreSQL 19 Beta 4 in the Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/postgresql-19-beta-4-amazon-rds-database-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for PostgreSQL now supports PostgreSQL 19 Beta 4 in the Preview Environment for enhanced query performance and stability.
+2. Outcome (impact):  
+Users can evaluate PostgreSQL 19 Beta 4's improved query performance, autovacuum management, and bug fixes before its official release.
+3. Where to use (use case):  
+Ideal for database administrators and developers looking to test new PostgreSQL features and improvements in a controlled environment.</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL now supports post-quantum TLS key exchange</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/postgresql-post-quantum-tls-key-exchange/</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for PostgreSQL now supports post-quantum TLS key exchange, enhancing data-in-transit encryption with quantum-resistant cryptography.
+2. Outcome (impact):
+This update provides enhanced security against future quantum computing threats, ensuring data encryption remains robust and future-proof.
+3. Where to use (use case):
+Ideal for organizations requiring high-security standards for data in transit, such as financial services, healthcare, and government sectors.</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>AWS Network Security Manager is now generally available in US East (N. Virginia) Region</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/network-security-manager-us-east-va/</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Network Security Manager is now available in the US East (N. Virginia) region, offering automated deployment and management of security policies across AWS environments.
+2. Outcome (impact):  
+Simplifies security policy deployment and enforcement, reduces operational overhead, and ensures consistent security posture across AWS accounts and resources.
+3. Where to use (use case):  
+Ideal for organizations needing to enforce firewall and DDoS protection configurations at scale across their AWS environment, particularly for internet-facing assets like AWS Application Load Balancer and Amazon CloudFront.</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>AWS Network Security Manager</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod Inference Gateway for scalable LLM inference</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sagemaker-hyperpod-inference-gateway/</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker HyperPod Inference Gateway enhances large language model (LLM) inference by providing intelligent routing, reducing latency and improving performance.
+2. Outcome (impact):
+Reduces first-token latency by up to 82% and p99 TTFT reductions of 97–98%, leading to faster and more efficient model inference.
+3. Where to use (use case):
+Ideal for deploying scalable and efficient LLM inference in applications requiring low-latency responses, such as real-time chatbots, recommendation systems, and other AI-driven services.</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>Run interactive workloads on Amazon EMR on EKS with Spark Connect</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/emr-eks-spark-connect-interactive/</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR on EKS now supports interactive Apache Spark sessions with Spark Connect, enabling data engineers and scientists to develop and debug Spark applications interactively.
+2. Outcome (impact):
+This update allows for more efficient and interactive development of Spark applications, facilitating ad hoc data exploration and incremental job development before production deployment.
+3. Where to use (use case):
+Ideal for data engineers and data scientists working on Spark applications, particularly in environments where they need to blend local Python code execution with remote Spark operations.</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Amazon EMR on EKS</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers now available in 5 new regions and 8 Local Zones</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-gamelift-servers-region-expansion-2026</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Servers are now available in 5 new regions and 8 Local Zones, enhancing latency reduction and gameplay responsiveness for global players.
+2. Outcome (impact):
+This expansion allows game developers to deploy game server fleets closer to players worldwide, significantly reducing latency and improving the overall gaming experience.
+3. Where to use (use case):
+Ideal for multiplayer game developers aiming to provide a smoother, more responsive gaming experience by deploying servers closer to their player base across various regions.</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache Global Datastore now supports tagging and tag-based access control</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-elasticache-global-datastore-tagging/</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ElastiCache Global Datastore now supports tagging and tag-based access control, enabling consistent permissions and cost allocation across regions.
+2. Outcome (impact):
+   This update allows for streamlined management of permissions and cost allocation for Global Datastores, enhancing security and operational efficiency.
+3. Where to use (use case):
+   Ideal for organizations that need to manage permissions and costs across multiple regions in a consistent and scalable manner.</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>Amazon RDS supports Multi-AZ for SQL Server Developer Edition</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-sql-server-multi-az-developer-edition/</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS now supports Multi-AZ deployments for SQL Server Developer Edition using Always On Availability Groups, enabling high availability testing without Enterprise Edition licensing costs.
+2. Outcome (impact):  
+Developers can validate high availability architectures and test failover behavior in non-production environments at no additional cost.
+3. Where to use (use case):  
+Ideal for testing and developing high availability configurations in non-production environments without incurring Enterprise Edition licensing fees.</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -46547,7 +46991,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:18:38</t>
+          <t>2026-09-25 08:42:11</t>
         </is>
       </c>
     </row>
@@ -46558,7 +47002,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -46568,7 +47012,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2186</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="7">
@@ -46578,7 +47022,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>700</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="8">
@@ -46588,7 +47032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000155</v>
+        <v>0.000306</v>
       </c>
     </row>
     <row r="9">
@@ -46598,7 +47042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000199</v>
+        <v>0.000433</v>
       </c>
     </row>
     <row r="10">
@@ -46608,7 +47052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000354</v>
+        <v>0.000739</v>
       </c>
     </row>
     <row r="11">
@@ -46618,7 +47062,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.076978</v>
+        <v>0.07771699999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1254"/>
+  <dimension ref="A1:F1263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -46926,6 +46926,345 @@
       <c r="F1254" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>Amazon Transcribe adds customer-managed KMS keys for custom resources</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-transcribe/</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 19:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Transcribe now allows encryption of custom resources using customer-managed KMS keys, enhancing data security and control.
+2. Outcome (impact):
+   Users can now manage their own encryption keys for custom vocabularies, filters, and language models, providing greater security and compliance.
+3. Where to use (use case):
+   Ideal for organizations requiring strict control over their encryption keys for sensitive data, such as financial services, healthcare, and regulated industries.</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Amazon Transcribe</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8i and M8i-flex instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ec2-m8i-m8i-flex-thf/</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 18:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 M8i and M8i-flex instances are now available in the AWS European Sovereign Cloud (Germany) region, offering enhanced performance and price-performance.
+2. Outcome (impact):
+   Users can leverage up to 20% better performance for general-purpose workloads, with specific gains in databases, web applications, and AI deep learning models.
+3. Where to use (use case):
+   Ideal for web and application servers, microservices, data stores, virtual desktops, enterprise applications, and large-scale SAP workloads.</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8i and R8i-flex instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-r8i-r8i-flex-thf/</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 18:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 R8i and R8i-flex instances are now available in the AWS European Sovereign Cloud (Germany) region, offering enhanced performance and price-performance benefits for memory-intensive workloads.
+2. Outcome (Impact):
+- Up to 20% higher performance than R7i instances.
+- 15% better price-performance.
+- 2.5x more memory bandwidth.
+- Significant speed improvements for specific workloads like PostgreSQL, NGINX, and AI deep learning.
+3. Where to Use (Use Case):
+- Ideal for memory-intensive workloads such as databases (e.g., PostgreSQL), web applications (e.g., NGINX), and AI deep learning models.
+- Suitable for mission-critical SAP workloads due to SAP certification.</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8i and C8i-flex instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/c8i-c8i-flex-thf-september-2026/</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 18:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8i and C8i-flex instances, powered by custom Intel Xeon 6 processors, are now available in the AWS European Sovereign Cloud (Germany) region, offering improved performance and price-performance.
+2. Outcome (impact):
+   These instances provide up to 20% higher performance and up to 15% better price-performance compared to previous generations, with significant speed improvements for specific workloads.
+3. Where to use (use case):
+   - C8i-flex: Ideal for web and application servers, databases, caches, Apache Kafka, Elasticsearch, and enterprise applications.
+   - C8i: Best suited for memory-intensive workloads, large applications, and continuous high CPU usage.</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>AWS IAM outbound identity federation now supports interface VPC endpoints for OIDC discovery</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-sts-vpc-oidc/</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 17:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS IAM now supports VPC endpoints for OIDC discovery, enabling secure access to OIDC metadata and JWKS keys within VPCs.
+2. Outcome (impact):
+   Enhances security by keeping verification key retrieval traffic within the AWS network, meeting network security requirements for restricted VPCs.
+3. Where to use (use case):
+   Ideal for workloads in VPCs with restricted internet access that need to verify JWTs from external services without exposing traffic to the public internet.</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>IAM</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>AWS DataSync launches a monitoring dashboard for tracking task executions across your account</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/datasync-monitoring-dashboard</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 15:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS DataSync introduces a monitoring dashboard for tracking task executions, providing visibility into data transfers across your account.
+2. Outcome (impact):  
+Easily monitor the health, performance, and progress of multiple data transfer tasks from a single view, simplifying troubleshooting and management.
+3. Where to use (use case):  
+Ideal for large-scale data migrations and recurring transfers involving multiple tasks, ensuring efficient tracking and issue resolution.</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>DataSync</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery now supports AWS Graviton-based source servers</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/elastic-disaster-recovery-graviton/</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elastic Disaster Recovery now supports AWS Graviton-based source servers, enabling seamless disaster recovery for arm64 workloads.
+2. Outcome (impact):  
+Ensures Graviton workloads receive the same disaster recovery coverage as x86 workloads, enhancing reliability and continuity for price-performance-driven architectures.
+3. Where to use (use case):  
+Ideal for organizations migrating to AWS Graviton instances for cost and performance benefits, requiring comprehensive disaster recovery solutions.</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging now supports voice calling on WhatsApp</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-end-user-messaging-voice-calling-whatsapp</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS End User Messaging now supports voice calling on WhatsApp, allowing seamless transitions from chat to voice within the same messaging thread.
+2. Outcome (impact):
+Enhances customer engagement by providing a unified communication experience, improving customer service efficiency and satisfaction.
+3. Where to use (use case):
+Businesses can use this feature to handle customer support, sales, and other interactions directly within WhatsApp, maintaining context and reducing the need for switching applications.</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging and Amazon SES now offer AI agent skills for the AWS MCP Server</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-messaging-ses-ai-skills-mcp-server/</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS End User Messaging and Amazon SES now offer AI agent skills for the AWS MCP Server, allowing developers to build and send messages using natural language commands.
+2. Outcome (impact):
+These skills streamline messaging workflows by providing step-by-step guidance through AI coding agents, reducing the need for manual documentation searches and console navigation.
+3. Where to use (use case):
+Use these skills to verify sending identities, build branded Rich Communication Services (RCS) agents, and send production emails directly through natural language commands.</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Service Name: AWS End User Messaging, Amazon SES  
+Category: Developer Tools</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -46991,7 +47330,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 08:42:11</t>
+          <t>2026-09-26 08:28:08</t>
         </is>
       </c>
     </row>
@@ -47002,7 +47341,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -47012,7 +47351,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4307</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="7">
@@ -47022,7 +47361,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1525</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="8">
@@ -47032,7 +47371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000306</v>
+        <v>0.000249</v>
       </c>
     </row>
     <row r="9">
@@ -47042,7 +47381,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000433</v>
+        <v>0.000351</v>
       </c>
     </row>
     <row r="10">
@@ -47052,7 +47391,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000739</v>
+        <v>0.000599</v>
       </c>
     </row>
     <row r="11">
@@ -47062,7 +47401,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07771699999999999</v>
+        <v>0.078316</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1263"/>
+  <dimension ref="A1:F1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -47265,6 +47265,339 @@
       <c r="F1263" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Future-dated Capacity Reservations Now Supports Postponing Start Dates</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-fcr-postpone-start-date/</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 21:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 now allows users to postpone the start dates of future-dated Capacity Reservations, with a quote for the new terms.
+2. Outcome (impact):
+This update provides flexibility for users to adjust their capacity plans without losing their reservations, potentially saving costs and resources.
+3. Where to use (use case):
+Ideal for scenarios where project timelines change, such as seasonal business needs, unexpected delays, or budget adjustments.</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>Amazon Rekognition Face Liveness now returns Feedback Codes</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/rekognition-liveness-feedback-codes/</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 20:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Rekognition Face Liveness now provides Feedback Codes to help users understand and resolve issues causing low liveness check scores.
+2. Outcome (impact):  
+Customers can more effectively troubleshoot and improve their liveness check results, enhancing the accuracy and user experience of identity verification processes.
+3. Where to use (use case):  
+Ideal for identity verification onboarding, re-authentication flows, and scenarios requiring robust accessibility in verifying user identities.</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Amazon Rekognition Face Liveness</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>Grok 4.7 is now available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-grok-4-7/</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 18:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Bedrock now supports SpaceXAI Grok 4.7, enhancing coding, agentic tasks, and knowledge work with improved features.
+2. Outcome (Impact):
+   Users can leverage advanced coding assistance, better document handling, and enhanced browser-use agents for more efficient and reliable task automation.
+3. Where to Use (Use Case):
+   Ideal for software developers, data scientists, and knowledge workers needing robust coding support, document processing, and automated web interactions.</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5.5 now available on AWS</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-sonnet-5-5-aws/</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now offers the enhanced Claude Sonnet 5.5, delivering improved efficiency and cost-effectiveness for coding and knowledge work.
+2. Outcome (impact):
+Increased productivity and cost savings for teams using AWS for coding and knowledge work tasks.
+3. Where to use (use case):
+Coding assistance, task automation, document creation, and data cleanup in software development and knowledge management.</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5.5 now available on AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-sonnet-5-5-aws-govcloud-us/</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS GovCloud (US) now offers the enhanced Claude Sonnet 5.5, providing smarter and more efficient coding and knowledge work capabilities at a lower cost per task.
+2. Outcome (Impact):
+Teams can achieve faster and more efficient coding and knowledge work, reducing costs while enhancing productivity and output quality.
+3. Where to Use (Use Case):
+Ideal for teams engaged in coding, software development, documentation, and other knowledge work tasks that require precision and efficiency.</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>Amazon Corretto September 2026 Patch Updates</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-corretto-sept-2026-updates/</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has released patch updates for Corretto 25, 21, 17, and 11 on September 25, 2026, including the latest tzdata 2026d updates.
+2. Outcome (impact):
+These updates ensure that your Java applications remain secure and up-to-date with the latest time zone data.
+3. Where to use (use case):
+Ideal for production environments running Java applications that require the latest security patches and time zone data.</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Amazon Corretto</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB (with MongoDB compatibility) now supports retryable writes</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-documentdb-retryable-writes/</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon DocumentDB now supports retryable writes starting with engine version 8.0.2, enhancing application resilience during transient errors.
+2. Outcome (impact)
+This update improves application resilience by automatically retrying certain write operations on transient errors, reducing the need for manual error handling.
+3. Where to use (use case)
+Ideal for MongoDB-compatible applications requiring high availability and resilience against transient errors like network interruptions or primary failovers.</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB (with MongoDB compatibility) adds support for 5 MongoDB aggregation stages and change stream capabilities in version 8.0.2</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-documentdb-8-0-2/</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DocumentDB now supports retryable writes, 5 new aggregation stages, and enhanced change streams in version 8.0.2, improving migration and query performance for MongoDB workloads.
+2. Outcome (impact):
+   This update enhances the compatibility and functionality of Amazon DocumentDB with MongoDB, making it easier to migrate applications with minimal code changes and improving overall query performance and resilience.
+3. Where to use (use case):
+   Ideal for applications requiring advanced analytics, faceted search, hierarchical queries, and improved resilience during failovers, such as e-commerce platforms, real-time analytics dashboards, and high-availability applications.</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>AWS Backup adds logically air-gapped vault support for Amazon FSx for NetApp ONTAP</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-backup-air-gapped-vault-fsx-ontap/</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Backup now supports logically air-gapped vaults for Amazon FSx for NetApp ONTAP, enhancing security and disaster recovery.
+2. Outcome (impact):
+This update allows secure sharing of backups across accounts and regions, reducing recovery time and ensuring business continuity.
+3. Where to use (use case):
+Ideal for organizations needing to meet compliance and disaster recovery requirements by securely storing and managing FSx for NetApp ONTAP backups.</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -47330,7 +47663,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26 08:28:08</t>
+          <t>2026-09-29 09:39:38</t>
         </is>
       </c>
     </row>
@@ -47351,7 +47684,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3503</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="7">
@@ -47361,7 +47694,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1235</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="8">
@@ -47371,7 +47704,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000249</v>
+        <v>0.000221</v>
       </c>
     </row>
     <row r="9">
@@ -47381,7 +47714,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000351</v>
+        <v>0.000312</v>
       </c>
     </row>
     <row r="10">
@@ -47391,7 +47724,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000599</v>
+        <v>0.000532</v>
       </c>
     </row>
     <row r="11">
@@ -47401,7 +47734,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.078316</v>
+        <v>0.078848</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1272"/>
+  <dimension ref="A1:F1288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -47598,6 +47598,610 @@
       <c r="F1272" t="inlineStr">
         <is>
           <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Agents, powered by OpenAI, is now available in preview</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/bedrock-managed-agents-preview/</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 21:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS and OpenAI have launched Amazon Bedrock Managed Agents (BMA) in preview, enabling users to build and manage AI agents within AWS using customized Agents API.
+2. Outcome (impact):
+   Users can now create and deploy AI agents optimized for specific tasks, leveraging AWS's governance, identity, and permission controls, while maintaining state and session continuity.
+3. Where to use (use case):
+   Ideal for automating complex workflows, integrating with various tools, and managing multi-step processes within AWS environments, such as customer service bots, data processing agents, and more.</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>Amazon RDS now adds full snapshot size information to the Console and API</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-full-snapshot-size-available/</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 21:00:23 GMT</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS now shows the complete size of database snapshots, including all blocks, via the console and API.
+2. Outcome (impact):  
+Users can now programmatically and visually access the total size of all blocks in a snapshot, aiding in better storage management and cost estimation.
+3. Where to use (use case):  
+Ideal for database administrators and cloud architects who need to understand the true storage footprint of their snapshots for planning and cost analysis.</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-6.1 Sol is now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/openai-gpt-6-1-sol-on-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 20:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched GPT-6.1 Sol from OpenAI on Amazon Bedrock, enhancing agentic coding and professional work capabilities at a lower cost.
+2. Outcome (impact):
+Developers can now build and run scalable, capable agents with improved performance and cost efficiency, leveraging advanced AI for complex tasks.
+3. Where to use (use case):
+Use GPT-6.1 Sol for building features, debugging, iterating on solutions, executing multistep workflows, and investigating complex codebases.</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now lets business users manage more reference data to adjust contact center configurations in real time</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-manage-data-tables/</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now allows administrators to manage up to 20,000 values per data table for real-time contact center configurations, with enhanced data management capabilities.
+2. Outcome (impact):
+Business users can now independently manage and update contact center configurations, improving efficiency and reducing dependency on technical teams.
+3. Where to use (use case):
+Ideal for contact centers needing dynamic and real-time adjustments to operating hours, escalation rules, AI prompts, and queue assignments.</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications introduces unified graphics images</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-workspaces-applications-unified-graphics-images/</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon WorkSpaces Applications introduces unified graphics images for simplified management across all supported instance families.
+2. Outcome (impact):
+   This update simplifies image management, streamlines the adoption of newer GPU generations, and allows for flexible instance type changes across different graphics instance families.
+3. Where to use (use case):
+   Ideal for organizations managing multiple graphics-intensive workloads, enabling easier updates and optimizations of their WorkSpaces fleets.</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>AWS Service Availability Updates</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-service-availability/</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 16:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS is updating its service availability, moving some to maintenance, sunsetting others, and ending support for certain services.
+2. Outcome (Impact):
+Customers using affected services need to plan migrations and transitions to avoid disruptions. Existing users can continue using the services until the specified dates.
+3. Where to Use (Use Case):
+- Amazon Chime SDK SIP Media Application: Real-time communication solutions.
+- Amazon WorkSpaces Secure Browser: Secure web browsing for enterprise applications.
+- Amazon Managed Blockchain: Blockchain network management.
+- Amazon DevOps Guru: Operational insights and issue detection.
+- AWS Backint Agent for SAP ASE: SAP ASE backup and recovery.
+- AWS Infrastructure Composer: Infrastructure as code templates.
+- Amazon Mechanical Turk: Human intelligence tasks.
+AWS Service: Amazon WorkSpaces Secure Browser | Category: Security
+AWS Service: Amazon Managed Blockchain | Category: Other
+AWS Service: Amazon DevOps Guru | Category: Management
+AWS Service: AWS Backint Agent for SAP ASE | Category: Other
+AWS Service: AWS Infrastructure Composer | Category: Management
+AWS Service: Amazon Mechanical Turk | Category: Other</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Amazon Chime SDK SIP Media Application</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL announces Extended Support minor versions 13.23-rds.20260514, 12.22-rds.20260514 and 11.22-rds.20260514</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-postgresql-extended-support/</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for PostgreSQL introduces Extended Support minor versions 13.23, 12.22, and 11.22, extending critical fixes by up to three years.
+2. Outcome (impact):
+Users gain more time to upgrade to newer major versions while receiving critical security and bug fixes.
+3. Where to use (use case):
+Ideal for organizations needing extended security and stability for their PostgreSQL databases without immediate major version upgrades.</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>Amazon Aurora now supports PostgreSQL 18.6, 17.11, 16.15, 15.19, 14.24</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-aurora-postgresql-18-6-17-11-16-15-15-19-14-24/</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora PostgreSQL now supports versions 18.6, 17.11, 16.15, 15.19, and 14.24 with bug fixes and enhancements.
+2. Outcome (impact):
+Users can benefit from improved performance, security fixes, and new features, ensuring their databases are up-to-date and secure.
+3. Where to use (use case):
+Ideal for applications requiring high availability, scalability, and security, such as e-commerce platforms, financial services, and enterprise applications.</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock expands Claude model availability to India, South Korea, and Singapore</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-region-expansion-in-sk/</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 15:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Bedrock now offers Anthropic's Claude models in India, South Korea, and Singapore, enabling in-country data processing for compliance.
+2. Outcome (Impact):
+   Enhanced data residency and compliance capabilities for customers in India, South Korea, and Singapore, particularly in regulated sectors like finance and healthcare.
+3. Where to Use (Use Case):
+   Ideal for financial services, healthcare, and public sector organizations needing to process data within specific geographic boundaries.</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>AWS Transform now supports Apache Kafka migration assessments for Amazon MSK</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-msk-migration-assessment-with-aws-transform</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now offers agentic migration assessments for moving on-premises Apache Kafka clusters to Amazon MSK, providing compatibility checks, broker sizing, and cost projections.
+2. Outcome (impact):
+Accelerates Kafka-to-MSK migration planning by automating compatibility checks, sizing recommendations, and cost projections, reducing manual effort and time from weeks to minutes.
+3. Where to use (use case):
+Use this service to evaluate and plan the migration of existing Apache Kafka clusters to Amazon MSK, ensuring compatibility, optimizing resource usage, and preparing a cost-effective migration strategy.</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager now supports sharing documents through AWS Resource Access Manager</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/systems-manager-sharing-documents-ram/</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Systems Manager now allows sharing SSM Documents via AWS RAM with entire organizations or specific OUs, automating updates as accounts change.
+2. Outcome (impact):
+Eases document management and sharing within AWS organizations, reducing manual tracking and ensuring up-to-date access controls.
+3. Where to use (use case):
+Ideal for organizations needing streamlined document sharing across multiple AWS accounts, ensuring consistent access management and compliance.</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>AWS DataSync now supports shared VPCs</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-datasync-shared-vpcs/</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS DataSync now supports shared VPCs, allowing data transfer over shared subnets and VPC endpoints across multiple accounts, reducing IP address consumption and operational overhead.
+2. Outcome (impact):
+   This update conserves IP address space, simplifies management by eliminating the need for per-account VPC endpoints, and reduces operational overhead for centralized networking setups.
+3. Where to use (use case):
+   Ideal for organizations with centralized networking that need to transfer data across multiple AWS accounts using a single VPC endpoint, enhancing efficiency and resource management.</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>AWS DataSync</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family now supports downloading multiple files and folders in web apps</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/transfer-family-web-apps-download-multiple-files-folders</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Transfer Family now enables web app users to download multiple files and folders simultaneously as a zip archive.
+2. Outcome (impact):  
+   This update enhances user efficiency by allowing bulk downloads, preserving folder structures, and providing real-time progress updates.
+3. Where to use (use case):  
+   Ideal for web applications requiring bulk file management, such as content management systems, data archival, and collaborative workspaces.</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache Serverless for Valkey now supports public endpoints</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-elasticache-serverless-public-endpoints/</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ElastiCache Serverless for Valkey now supports public endpoints, enabling direct internet access to your cache without VPC configuration.
+2. Outcome (impact):
+Simplifies cache access for prototyping, AI tools integration, and workloads outside AWS VPC, enhancing flexibility and speed.
+3. Where to use (use case):
+Ideal for rapid prototyping, connecting AI coding tools directly to the cache, and adding caching to non-VPC accessible workloads.</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver DNS Firewall support for Palo Alto Networks Advanced DNS Security is now Generally Available (GA)</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/route-53-dns-firewall-panw-dns-security-generally-available</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 01:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Route 53 Resolver DNS Firewall now supports Palo Alto Networks Advanced DNS Security, enabling DNS threat protection across 32 AWS Regions.
+2. Outcome (impact):  
+Security teams can detect and block malicious DNS traffic directly from their VPCs using PANW rules without additional firewalls or VPC modifications.
+3. Where to use (use case):  
+Ideal for securing DNS traffic in Amazon VPCs and hybrid cloud environments, protecting against threats like Command and Control, Malware, Phishing, etc.</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Route 53 DNS Firewall</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports two new connection capabilities: Iceberg REST Catalog connections and IAM authentication for Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sagemaker-iceberg-rest-iam-documentdb/</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now supports Iceberg REST Catalog connections and IAM authentication for Amazon DocumentDB, enhancing data connectivity and security.
+2. Outcome (impact):
+Data teams can now connect to a broader set of governed data sources and use credential-less authentication, improving data management and security.
+3. Where to use (use case):
+Use these features for data exploration, ETL processes, and querying data from external Apache Iceberg catalogs and Amazon DocumentDB in a secure manner.</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -47663,7 +48267,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 09:39:38</t>
+          <t>2026-09-30 09:31:33</t>
         </is>
       </c>
     </row>
@@ -47674,7 +48278,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -47684,7 +48288,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3107</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="7">
@@ -47694,7 +48298,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1097</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="8">
@@ -47704,7 +48308,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000221</v>
+        <v>0.000438</v>
       </c>
     </row>
     <row r="9">
@@ -47714,7 +48318,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000312</v>
+        <v>0.00061</v>
       </c>
     </row>
     <row r="10">
@@ -47724,7 +48328,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000532</v>
+        <v>0.001048</v>
       </c>
     </row>
     <row r="11">
@@ -47734,7 +48338,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.078848</v>
+        <v>0.07989599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1288"/>
+  <dimension ref="A1:F1311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -48200,6 +48200,858 @@
         </is>
       </c>
       <c r="F1288" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Core Managed Instances adds support for NVIDIA Blackwell GPU</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-workspaces-cmi-g7/</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 23:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces Core Managed Instances now support Graphics G7 instances with enhanced performance for graphics-intensive workloads.
+2. Outcome (impact):
+Customers can achieve up to 2.1X better performance for applications like CAD, 3D rendering, and AI-assisted design, with higher fidelity and frame rates.
+3. Where to use (use case):
+Ideal for professional applications requiring high-performance graphics, such as CAD/CAM, 3D rendering, scientific visualization, video editing, and AI-assisted design.</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Core</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>AWS CLI now supports bulk skill updates and version checks for the Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-cli-agent-toolkit-update-skill/</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 20:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CLI now supports bulk skill updates and version checks for the Agent Toolkit, streamlining the process of keeping agent skills current.
+2. Outcome (impact):
+This update allows developers to efficiently manage and update multiple agent skills simultaneously, reducing manual effort and ensuring agents operate with the latest guidance.
+3. Where to use (use case):
+Ideal for teams managing numerous skills across various domains like serverless, storage, networking, and analytics, ensuring their coding agents are always up-to-date.</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors introduces metadata pre-filtering for up to 5x higher recall on filtered search</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/s3-vectors-introduces-metadata-pre-filtering/</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Vectors now offers metadata pre-filtering to enhance search recall by up to 5x and includes a new prefix match operator for more precise filtering.
+2. Outcome (impact):
+Improved search accuracy and relevance for retrieval-augmented generation (RAG), agentic, and semantic-search applications by returning more matching vectors when filters are applied.
+3. Where to use (use case):
+Ideal for applications requiring precise vector searches, such as content recommendation systems, semantic search engines, and intelligent document retrieval systems.</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana now supports creating Grafana 13.2 workspaces</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-managed-grafana-now-supports-creating-grafana-13-2-workspaces</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 19:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Managed Grafana now supports Grafana 13.2 workspaces, introducing Git Sync, dynamic dashboards, and PromQL query support.
+2. Outcome (Impact):  
+   Enhanced version control, adaptability in dashboard layouts, and improved querying capabilities for CloudWatch metrics.
+3. Where to Use (Use Case):  
+   Ideal for teams needing better version control and dynamic dashboard capabilities, as well as those leveraging Prometheus Query Language for querying CloudWatch metrics.</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-6 Astra now supports UltraFast mode on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/openai-gpt-6-astra-ultrafast-on-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces UltraFast mode for GPT-6 Astra on Amazon Bedrock, offering up to 6x faster inference for latency-sensitive applications.
+2. Outcome (Impact):
+This enhancement allows for significantly faster response times in applications requiring real-time interactions, improving user experience and efficiency.
+3. Where to Use (Use Case):
+Ideal for real-time coding assistants, interactive agents, and customer-facing experiences that demand quick, high-quality responses.</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service now supports scaling logs</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-pcs-scaling-logs/</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS PCS now supports scaling logs to help troubleshoot compute node scaling issues, available in all AWS Regions.
+2. Outcome (impact):
+Easier troubleshooting of scaling issues by providing detailed logs of compute node state transitions.
+3. Where to use (use case):
+Use scaling logs to identify and resolve issues such as failed launches, node registration problems, and scale-down events in HPC workloads.</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service (AWS PCS)</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>Amazon Aurora serverless now scales faster to support agentic AI and other bursty workloads</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aurora-serverless-instant-16-acu-scaling/</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 17:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora serverless now scales up to 16 ACUs per second and up to 256 ACUs, ideal for bursty workloads like agentic AI.
+2. Outcome (impact):
+   Faster scaling for bursty workloads, reducing latency and improving performance for applications with unpredictable traffic patterns.
+3. Where to use (use case):
+   Ideal for agentic AI applications, microservices, and other applications with bursty and unpredictable workloads.</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>Amazon Aurora and RDS now support AMD-based R8a instances</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aurora-rds-amd-r8a/</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Aurora and RDS now support AMD-based R8a instances, offering high performance and bandwidth for database workloads.
+2. Outcome (Impact):  
+Users can leverage enhanced performance and I/O capabilities for their database instances, improving efficiency and throughput for demanding applications.
+3. Where to Use (Use Case):  
+Ideal for high-performance database workloads, such as large-scale transactional databases, data analytics, and applications requiring high I/O operations.</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon RDS  
+Category: Database</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports AMD-based M8a instances</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aurora-rds-amd-m8a/</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS now offers M8a instances with AMD EPYC processors for PostgreSQL, MySQL, and MariaDB, enhancing performance and I/O capabilities.
+2. Outcome (impact):
+   Users can leverage high-performance, cost-effective database instances for demanding workloads across multiple regions.
+3. Where to use (use case):
+   Ideal for database-intensive applications requiring high I/O performance and consistent per-core performance, such as e-commerce platforms, financial services, and large-scale data analytics.</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock expands Claude models in-region support in the UK (London)</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-region-expansion-lhr/</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Bedrock now supports Anthropic's Claude Opus 5.5 and Sonnet 5 models in the UK (London) Region, enabling in-country data processing.
+2. Outcome (impact):  
+   Customers in the UK, particularly in sensitive sectors like finance, healthcare, and public services, can now leverage advanced AI models while ensuring data remains within the country.
+3. Where to use (use case):  
+   Ideal for financial services, healthcare, and public sector organizations needing to comply with data residency regulations.</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Aurora PostgreSQL now supports querying of Apache Iceberg and Parquet data</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aurora-postgresql-query-apache-iceberg-and-parquet/</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Aurora PostgreSQL now allows direct querying of Apache Iceberg and Parquet data in Amazon S3 without ETL processes or data duplication.
+2. Outcome (impact):
+This update enables cost savings and reduces engineering effort by eliminating the need for ETL pipelines, allowing seamless access to data lakes directly from PostgreSQL applications.
+3. Where to use (use case):
+Ideal for businesses needing to integrate data lake insights with operational data for informed decision-making and process automation, without data duplication or costly ETL processes.</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL supports MySQL 26.7 in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/rds-mysql-26-7-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for MySQL now supports MySQL 26.7 in the Preview Environment, featuring new innovations and a new versioning model.
+2. Outcome (impact):
+Users can test MySQL 26.7's new features and improvements, ensuring compatibility and performance before general release.
+3. Where to use (use case):
+Ideal for development and testing environments to evaluate new MySQL features and enhancements in a controlled setting.</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Uncover blind spots in AWS data plane operations with CloudTrail Event Coverage</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-cloudtrail-event-coverage/</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CloudTrail's Event Coverage offers visibility into data plane operations, highlighting which services have data event logging enabled and which do not.
+2. Outcome (impact):
+Event Coverage helps organizations quickly identify and close gaps in their logging posture, reducing blind spots in security monitoring and improving detection of unauthorized data access.
+3. Where to use (use case):
+Ideal for organizations managing multiple AWS accounts, ensuring comprehensive data event logging across all services to enhance security monitoring and compliance.</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>AWS CloudTrail</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Partner Revenue Measurement adds Multi-Partner support to Resource Tagging</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/partner-revenue-measurement-multi-partner-resource-tagging</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   PRM now supports multi-Partner resource tagging, allowing multiple Partners to receive revenue attribution for the same AWS resource.
+2. Outcome (impact):
+   Partners collaborating on a project can now both receive revenue attribution, improving collaboration and revenue tracking accuracy.
+3. Where to use (use case):
+   Ideal for consulting and software Partners working together on deploying solutions in a shared AWS account.</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Partner Revenue Measurement</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>AWS accounts now support phone number verification</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-accounts-phone-number-verification/</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS now verifies primary contact phone numbers via SMS OTP, enhancing account security and contact reliability.
+2. Outcome (impact):
+   Improved security and reliability of contact information, reducing the risk of unauthorized access and ensuring accurate communication.
+3. Where to use (use case):
+   Ideal for organizations that require secure and verified contact information for compliance, billing, and support purposes.</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>AWS Account Management</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family now automatically approves SFTP connector quota increases up to 1,000</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-transfer-family-sftp-connector-quota-1000/</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transfer Family now automatically approves SFTP connector quota increases up to 1,000 per account and region, streamlining scaling without manual intervention.
+2. Outcome (Impact):  
+Users can scale their SFTP connectors more efficiently, reducing wait times and improving operational agility.
+3. Where to Use (Use Case):  
+Ideal for organizations with growing file transfer needs, such as large enterprises or businesses expanding their cloud-based file transfer operations.</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center Identity Store APIs now accept resource ARNs in addition to resource IDs</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/iam-identity-center-apis-arns/</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM Identity Center's Identity Store APIs now support both ARNs and IDs, simplifying application code and reducing parsing errors.
+2. Outcome (impact):
+This update eliminates the need to convert ARNs to IDs before API calls, making application code simpler and more reliable.
+3. Where to use (use case):
+Use this feature in applications that integrate with IAM policy evaluation, CloudTrail events, or cross-service integrations to streamline resource handling.</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>AWS Marketplace launches an AI agent skill for usage-based metering integration</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/marketplace-ai-agent-metering/</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces an AI-guided skill for seamless SaaS usage-based metering integration in AWS Marketplace, simplifying the setup process and reducing common errors.
+2. Outcome (impact):
+   The metering agent skill reduces the complexity of integrating usage-based metering, minimizes errors, and accelerates the deployment process for sellers, ensuring accurate billing and smoother operations.
+3. Where to use (use case):
+   SaaS providers looking to implement usage-based (pay-as-you-go) billing models in AWS Marketplace can utilize this skill to efficiently integrate and validate their metering solutions.</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Amazon S3 Tables now support all Apache Iceberg V3 data types</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-s3-tables-iceberg-v3-data-types</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Tables now fully support Apache Iceberg V3 data types, including geometry, geography, unknown, and nanosecond timestamps, enhancing geospatial and high-precision time data handling.
+2. Outcome (impact):
+This update simplifies data architecture, improves storage efficiency, and enhances performance for geospatial and high-precision time data workloads.
+3. Where to use (use case):
+Ideal for fleet tracking, asset mapping, telemetry, and financial applications requiring precise geospatial coordinates and nanosecond-level timestamps.</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now supports expressions in job templates</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-deadline-cloud-expressions-job-templates/</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 21:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Deadline Cloud now supports expressions and advanced parameter types in job templates, enhancing automation and flexibility for compute-intensive workloads.
+2. Outcome (impact):  
+   This update allows customers to automate bespoke pipeline operations more effectively, leading to cleaner, more powerful workflows and better integration with existing production pipelines.
+3. Where to use (use case):  
+   Ideal for visual effects, animation, product design, simulation, and gaming teams that need to run compute-intensive workloads in the cloud.</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now supports ECS containers on Linux Service-Managed Fleets</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-deadline-cloud-ecs-containers-linux-smf/</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 20:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Deadline Cloud now supports ECS containers on Linux service-managed fleets, enabling efficient cloud-based compute-intensive workloads.
+2. Outcome (impact):  
+Customers can deploy containerized software directly to Deadline Cloud, streamlining workflows and accelerating the transition to managed render farms.
+3. Where to use (use case):  
+Ideal for visual effects, animation, product design, simulation, and gaming workloads that require containerized software.</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs now automatically indexes frequently queried fields</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/cloudwatch-logs-auto-indexes-fields/</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Logs now automatically indexes frequently queried fields, speeding up query performance without manual setup.
+2. Outcome (impact):
+   Faster CloudWatch Logs Insights queries and reduced manual effort as frequently queried fields are automatically indexed.
+3. Where to use (use case):
+   Ideal for teams with evolving query patterns, ensuring optimal query performance without manual index management.</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights now lets you estimate bytes scanned before running a query</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/cloudwatch-logs-estimate-bytes-scanned/</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Logs Insights now estimates query bytes before execution, aiding in cost-effective log management.
+2. Outcome (impact):
+   Users can optimize their log queries by adjusting log groups, time ranges, and filters based on byte estimates, potentially reducing costs and improving performance.
+3. Where to use (use case):
+   Ideal for developers and operations teams managing large log datasets to avoid unnecessary data scanning and associated costs.</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
@@ -48267,7 +49119,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:31:33</t>
+          <t>2026-10-01 09:58:17</t>
         </is>
       </c>
     </row>
@@ -48278,7 +49130,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -48288,7 +49140,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6169</v>
+        <v>8030</v>
       </c>
     </row>
     <row r="7">
@@ -48298,7 +49150,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2147</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="8">
@@ -48308,7 +49160,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000438</v>
+        <v>0.00057</v>
       </c>
     </row>
     <row r="9">
@@ -48318,7 +49170,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00061</v>
+        <v>0.000791</v>
       </c>
     </row>
     <row r="10">
@@ -48328,7 +49180,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001048</v>
+        <v>0.001361</v>
       </c>
     </row>
     <row r="11">
@@ -48338,7 +49190,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07989599999999999</v>
+        <v>0.081257</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1311"/>
+  <dimension ref="A1:F1334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -49054,6 +49054,860 @@
       <c r="F1311" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>GuardDuty Runtime Monitoring is now included in the AWS Security Hub Threat Analytics plan</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-security-hub-runtime-monitoring/</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 03:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   GuardDuty Runtime Monitoring is now included in the AWS Security Hub Threat Analytics plan, streamlining billing and coverage.
+2. Outcome (impact):
+   Customers with Security Hub enabled will no longer receive separate GuardDuty charges for Runtime Monitoring, simplifying their billing.
+3. Where to use (use case):
+   Ideal for monitoring threats on Amazon EC2 instances, Amazon EKS clusters, and Amazon ECS tasks on AWS Fargate.</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>AWS Well-Architected Agent is now available in preview</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-well-architected-agent/</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Well-Architected Agent, a preview AI-powered service, offers optimized recommendations for AWS infrastructure based on cost, security, performance, and reliability.
+2. Outcome (impact):
+Teams can prioritize and implement AWS Well-Architected best practices with automated fixes, SSM runbooks, and guided console walkthroughs, enhancing infrastructure efficiency and alignment with business goals.
+3. Where to use (use case):
+Use the AWS Well-Architected Agent to analyze and optimize AWS resources, applications, and architectures, ensuring they adhere to Well-Architected best practices and business priorities.</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>AWS Well-Architected Agent</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Amazon Redshift now supports cross-Region queries for your data lake</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/redshift-cross-Region-queries-for-data-lake</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 18:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now supports cross-Region queries for S3 data lakes with enhanced VPC routing, enabling secure, global data analytics.
+2. Outcome (impact):
+Enables global analytics, consolidated reporting, and compliance with data residency requirements without data replication.
+3. Where to use (use case):
+Ideal for enterprises with globally distributed data and those needing strict control over data movement, such as financial services, healthcare, and government.</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB introduces filtered export to Amazon S3</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-dynamodb-introduces-filtered-export/</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DynamoDB now offers filtered export to Amazon S3, allowing users to export specific items and attributes from tables for targeted analytics and data sharing.
+2. Outcome (impact):
+   This feature enhances data management by enabling precise data exports, reducing storage costs, and ensuring compliance with data governance policies.
+3. Where to use (use case):
+   Use filtered export for granular data recovery, moving specific data slices between accounts, and running targeted analytics while adhering to compliance rules.</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB Accelerator (DAX) is now available in additional Regions</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-dynamodb-accelerator/</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 16:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of Amazon DynamoDB Accelerator (DAX) to 17 new regions, enhancing performance and enabling local data residency.
+2. Outcome (impact):
+Customers can now achieve up to 10 times performance improvement for read-heavy DynamoDB workloads with minimal code changes, meeting local data residency requirements.
+3. Where to use (use case):
+Ideal for read-intensive and bursty workloads such as real-time bidding, gaming leaderboards, and retail product catalogs.</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB Accelerator (DAX)</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty now supports centralized management using AWS Organizations declarative policies</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/guardduty-org-enablement-policies/</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 16:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GuardDuty now supports centralized management through AWS Organizations policies, enabling consistent threat detection across all accounts and regions.
+2. Outcome (impact):
+   Centralized management of GuardDuty ensures uniform threat detection coverage across all accounts and regions, reducing the risk of configuration drift and enhancing security posture.
+3. Where to use (use case):
+   Ideal for organizations with multiple accounts and regions needing consistent security monitoring and management without manual intervention in each account.</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Amazon Corretto 8 September 2026 Patch Updates</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-corretto-8-sept-2026-updates/</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has released a patch update for Corretto 8u504, including tzdata 2026d updates, available for download on September 30, 2026.
+2. Outcome (impact):
+This update ensures that Corretto 8 users have the latest time zone data, enhancing accuracy and reliability for applications dependent on time zone information.
+3. Where to use (use case):
+Ideal for Java applications requiring precise time zone data, such as financial services, logistics, and global applications.</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Amazon Corretto</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Amazon S3 Object Lock variable retention with event holds is now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/s3-object-lock-variable-retention-event-holds-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Object Lock now supports variable retention with event holds in AWS GovCloud (US) Regions, enabling WORM protection for objects based on future events.
+2. Outcome (impact):
+This feature allows organizations to comply with event-based retention requirements, ensuring data is retained only for the required period after a specific event.
+3. Where to use (use case):
+Ideal for industries needing compliance with SEC Rule 17a-4(f), FINRA Rule 4511, and CFTC Regulation 1.31, such as financial services and legal sectors.</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>AWS Security Hub introduces remediation plans to prioritize and fix security exposures</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-security-hub-remediation-plans/</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Security Hub now offers remediation plans to address root causes of security exposures, prioritizing fixes to reduce risk efficiently.
+2. Outcome (impact):
+   This feature helps streamline security remediation by allowing fixes to underlying issues that resolve multiple related exposures, reducing overall risk and improving security posture.
+3. Where to use (use case):
+   Ideal for organizations looking to efficiently manage and prioritize security vulnerabilities in their AWS environment, ensuring critical issues are addressed first.</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family now supports custom CloudWatch log groups for managed workflows</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/transfer-family-custom-cloudwatch-log-groups/</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transfer Family now allows users to specify custom CloudWatch log groups for managed workflow execution logs, enabling better log organization and monitoring.
+2. Outcome (impact):
+This update enhances log management by allowing separate logging for each workflow, facilitating more precise monitoring and analysis of workflow executions.
+3. Where to use (use case):
+This feature is ideal for organizations that need to monitor and manage multiple workflows independently, enabling better tracking, troubleshooting, and compliance auditing.</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Catalog now supports table optimization, statistics, and crawlers for Apache Iceberg V3</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-glue-iceberg-v3-optimization/</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Data Catalog now supports optimization, statistics, and crawlers for Apache Iceberg V3 tables, enhancing query performance and storage efficiency.
+2. Outcome (impact):
+Users can now automatically maintain, optimize, and discover Iceberg V3 tables, leading to improved query performance and reduced storage costs.
+3. Where to use (use case):
+Ideal for data lakes requiring efficient querying and management of large-scale datasets using Iceberg V3 tables.</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Glue</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>AWS Budgets now supports email verification for notification subscribers</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-budgets/</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Budgets now verifies new email subscribers for budget alerts to ensure they receive notifications. Verification applies to new email addresses added from September 30, 2026, onward.
+2. Outcome (impact):
+   This update enhances security by ensuring that only verified email addresses receive budget alerts, reducing the risk of unauthorized access to sensitive financial information.
+3. Where to use (use case):
+   This feature is useful for organizations managing multiple budgets and needing to ensure that only authorized personnel receive budget alerts.</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>AWS Budgets</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>Serverless Storage on Amazon EMR Serverless now supports terabyte-scale shuffle</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/emr-serverless-terabyte-scale-shuffle/</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EMR Serverless now supports up to 1TB shuffle operations, enabling large-scale data processing without storage constraints.
+2. Outcome (impact):
+   This enhancement allows enterprise data teams to run production workloads processing terabyte-scale datasets, improving job reliability and success rates for complex analytical tasks.
+3. Where to use (use case):
+   Ideal for processing large table joins, complex aggregations on high-cardinality data, and memory-intensive operations in Apache Spark workloads.</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>Announcing DNS analytics and insights for Route 53 Global Resolver and DNS Firewall</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/route-53-dns-analytics-insights/</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Route 53 Global Resolver and DNS Firewall now offer DNS analytics and insights via Amazon CloudWatch integration, enhancing observability and security.
+2. Outcome (impact):  
+   Network administrators and security teams can monitor DNS query patterns, assess DNS Firewall effectiveness, detect anomalies, and optimize DNS performance.
+3. Where to use (use case):  
+   Ideal for monitoring DNS activities in enterprise networks, detecting security threats, and ensuring optimal DNS infrastructure performance.</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Route 53</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center extends multi-Region support to more AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-iam-identity-center-extends-multi-region-support-to-more-aws-regions</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS IAM Identity Center now supports multi-Region replication, enhancing user access resilience and application deployment flexibility.
+2. Outcome (impact):  
+   Improved resilience of user access to AWS accounts and streamlined application deployment across multiple regions.
+3. Where to use (use case):  
+   Organizations needing to maintain user access continuity and deploy applications across multiple regions for better business alignment and disaster recovery.</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>Improve your secrets security posture with actionable recommendations in the AWS Secrets Manager console</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-secrets-manager-security-posture-recommendations</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Secrets Manager now provides actionable security recommendations directly in the console to enhance your secrets management practices.
+2. Outcome (impact):
+Improved security posture and adherence to best practices for managing secrets, reducing potential vulnerabilities and compliance risks.
+3. Where to use (use case):
+Ideal for developers and DevOps teams managing application secrets, ensuring they follow best practices for secret encryption, rotation, and configuration.</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>Amazon S3 Tables now support up to 100 table buckets per AWS Region in an AWS account</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-s3-tables-table-bucket-increase</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon S3 Tables now support up to 100 table buckets per AWS Region, enabling the creation of up to 1 million tables per Region.
+2. Outcome (Impact)
+This increase allows for better organization and management of data by creating separate table buckets for different datasets, workloads, or teams with enhanced security and performance settings.
+3. Where to Use (Use Case)
+Ideal for data lakes requiring scalable and efficient storage and querying of tabular data, such as analytics, data warehousing, and large-scale data processing.</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>Apache Iceberg materialized views now support system-managed write protection</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/system-managed-iceberg-materialized-views</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 21:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces system-managed materialized views for Apache Iceberg, ensuring data consistency by restricting write access to AWS Glue.
+2. Outcome (impact):
+   Ensures materialized views remain unchanged regardless of who has write access to the underlying data, providing a consistent and reliable dataset.
+3. Where to use (use case):
+   Ideal for scenarios requiring consistent, precomputed query results across multiple engines, such as data analytics and reporting.</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>AWS Continuum for Penetration Testing now available in 6 additional Regions</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-continuum-penetration/</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 16:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Continuum for Penetration Testing is now available in six new regions to support localized security testing and meet data residency requirements.
+2. Outcome (impact):
+Organizations can now conduct penetration testing closer to their production environments, ensuring compliance with local regulations and enhancing security posture.
+3. Where to use (use case):
+- Vulnerability assessments
+- Compliance validation (e.g., PCI DSS, ISO 27001)
+- Continuous security posture evaluations</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>AWS Continuum for Penetration Testing</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>Amazon Quick adds Hierarchy Filter for guided dashboard drill-down</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/quick-hierarchy-filter</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick introduces a Hierarchy Filter to streamline dashboard navigation by allowing users to drill down through related dimensions like Region, Country, and City with a single control.
+2. Outcome (impact):
+   The Hierarchy Filter reduces clutter, simplifies navigation, and enables users to access data more efficiently with fewer clicks.
+3. Where to use (use case):
+   Ideal for dashboards that require multi-level dimensional analysis, such as retail sales dashboards where users need to explore sales data by Region, Country, and City.</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Amazon QuickSight</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports live data from your datasets in apps</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/live-data-in-apps</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick now enables live data integration in applications, ensuring real-time data reflection and enhanced business operations.
+2. Outcome (impact):
+   Facilitates intelligent, data-driven workflows with up-to-date insights, improving decision-making and operational efficiency.
+3. Where to use (use case):
+   Ideal for team portals, request handling, and approval processes that require real-time data visibility and actions.</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>Amazon Redshift simplifies access to secure logging with federated permissions</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/redshift-secure-logging-permissions/</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Redshift now allows data owners to grant specific identities access to unredacted secure logging records, enabling better troubleshooting and auditing while maintaining data protection.
+2. Outcome (impact):  
+This update enhances the ability to audit and troubleshoot queries on data protected by federated permissions without compromising data security, ensuring compliance and operational efficiency.
+3. Where to use (use case):  
+Ideal for scenarios where administrators and auditors need visibility into query logs for compliance and troubleshooting, without exposing sensitive data to unauthorized users.</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Service name: Amazon Redshift  
+Category: Database</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Video Streams now supports VPC endpoints with AWS PrivateLink</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/kinesis-video-streams-vpc-privatelink/</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Kinesis Video Streams now supports VPC endpoints with AWS PrivateLink, enabling secure, private video ingestion and playback.
+2. Outcome (impact):  
+Customers can securely ingest, store, and playback video content within their VPC without exposing it to the public internet.
+3. Where to use (use case):  
+Ideal for connected-camera or IoT video workloads in private subnets, ensuring compliance with strict security and network-isolation requirements.</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Video Streams</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -49119,7 +49973,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01 09:58:17</t>
+          <t>2026-10-02 09:34:18</t>
         </is>
       </c>
     </row>
@@ -49140,7 +49994,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8030</v>
+        <v>8182</v>
       </c>
     </row>
     <row r="7">
@@ -49150,7 +50004,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2784</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="8">
@@ -49160,7 +50014,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00057</v>
+        <v>0.000581</v>
       </c>
     </row>
     <row r="9">
@@ -49170,7 +50024,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000791</v>
+        <v>0.000798</v>
       </c>
     </row>
     <row r="10">
@@ -49180,7 +50034,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001361</v>
+        <v>0.001379</v>
       </c>
     </row>
     <row r="11">
@@ -49190,7 +50044,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.081257</v>
+        <v>0.082636</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1334"/>
+  <dimension ref="A1:F1342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -49908,6 +49908,305 @@
       <c r="F1334" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>Amazon ECS adds Amazon VPC Lattice support for blue/green, linear, and canary deployments</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-ecs-vpc-lattice-blue-green-deployments</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 20:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now integrates with Amazon VPC Lattice for enhanced deployment strategies, including blue/green, linear, and canary deployments.
+2. Outcome (impact):
+ECS users can now manage traffic shifts during deployments more effectively, ensuring smoother updates and quicker rollbacks if issues arise.
+3. Where to use (use case):
+Ideal for applications requiring controlled traffic management during updates, especially those using VPC Lattice for cross-VPC and cross-account service communication.</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>AWS Health introduces the version catalog for software lifecycle management</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-health-introduces-version-catalog-software-lifecycle-management</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 18:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Health introduces the version catalog to centralize lifecycle information for software versions across AWS services, enabling proactive management of upgrades and end-of-support risks.
+2. Outcome (impact):
+Customers can now proactively manage software version upgrades and mitigate end-of-support risks by building upgrade schedules and governance controls.
+3. Where to use (use case):
+IT teams and DevOps engineers can use the version catalog to plan and execute software version upgrades across multiple AWS services, ensuring applications remain secure and operational.</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>AWS Health</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL now supports partial indexes</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aurora-dsql-partial-indexes/</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora DSQL now supports partial indexes, allowing indexing of specific subsets of a table to improve query performance and reduce storage costs.
+2. Outcome (impact):
+- Enhanced query performance by indexing only relevant rows.
+- Reduced storage costs by minimizing the size of the index.
+- Efficiently manages large tables with a mix of active and historical data.
+3. Where to use (use case):
+- Ideal for tables with a small active working set and a large historical dataset, such as active orders vs. completed orders.
+- Useful for scenarios where only a subset of rows is frequently queried.</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>Amazon EKS and Amazon EKS Distro now support Kubernetes version 1.37</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-eks-distro-kubernetes-version-1-37</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EKS and EKS Distro now support Kubernetes version 1.37, featuring new APIs, dynamic resource allocation, and improved autoscaling.
+2. Outcome (impact):  
+Enhanced cluster management and resource optimization with new Kubernetes features, improved autoscaling, and better resource allocation.
+3. Where to use (use case):  
+Ideal for deploying scalable and efficient containerized applications requiring advanced resource management and autoscaling.</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>AWS Brazil automates distribution of non-Brazilian software product licenses to Brazilian customers</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-brazil-software-license-distribution/</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Brazil automates the distribution of SaaS licenses from non-Brazilian ISVs to Brazilian customers, handling invoicing, taxes, and payments.
+2. Outcome (Impact):  
+Easier and more efficient distribution of SaaS products to Brazilian customers, reducing manual processes and compliance burdens for ISVs.
+3. Where to Use (Use Case):  
+Ideal for non-Brazilian ISVs looking to expand their reach in the Brazilian market without managing local distribution complexities.</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>The AWS MCP Server is now available in six additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-mcp-server-six-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of the AWS MCP Server to six new regions, enhancing accessibility and reducing latency for developers globally.
+2. Outcome (impact):
+Developers in the new regions can now leverage the AWS MCP Server for seamless integration with AWS services, ensuring lower latency and compliance with data residency requirements.
+3. Where to use (use case):
+Ideal for development teams in the newly supported regions who need to provision infrastructure, inspect workloads, and debug failures with minimal latency.</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>AWS MCP Server</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>AgentCore Gateway supports private TLS certificates for VPC endpoints</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/agentcore-gateway-private-tls-vpc/</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AgentCore Gateway now supports private TLS certificates for VPC endpoints, enabling secure connections to private endpoints without an intermediate load balancer.
+2. Outcome (impact)
+   This feature allows secure connections to private endpoints in your VPC using certificates from your own private CA, enhancing security and simplifying setup.
+3. Where to use (use case)
+   Use this feature to securely connect to private endpoints in your VPC, such as those powered by Amazon VPC Lattice, without needing an intermediate Application Load Balancer.</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>AgentCore Gateway</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache for Valkey now supports OpenTelemetry metrics and detailed monitoring</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-elasticache-valkey-opentelemetry-metrics-detailed-monitoring</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ElastiCache for Valkey now supports OpenTelemetry metrics and detailed monitoring, offering enhanced observability and more frequent data collection.
+2. Outcome (impact):
+Improved monitoring capabilities allow for better detection and analysis of cluster performance issues, enabling quicker incident response and resource management.
+3. Where to use (use case):
+Ideal for scenarios requiring high-frequency monitoring and detailed analysis of Valkey cluster performance, such as real-time analytics, high-traffic applications, and environments needing advanced diagnostic insights.</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -49973,7 +50272,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 09:34:18</t>
+          <t>2026-10-03 09:01:07</t>
         </is>
       </c>
     </row>
@@ -49984,7 +50283,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -49994,7 +50293,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8182</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="7">
@@ -50004,7 +50303,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2811</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -50014,7 +50313,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000581</v>
+        <v>0.000214</v>
       </c>
     </row>
     <row r="9">
@@ -50024,7 +50323,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000798</v>
+        <v>0.000284</v>
       </c>
     </row>
     <row r="10">
@@ -50034,7 +50333,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001379</v>
+        <v>0.000498</v>
       </c>
     </row>
     <row r="11">
@@ -50044,7 +50343,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.082636</v>
+        <v>0.083134</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1342"/>
+  <dimension ref="A1:F1353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -50207,6 +50207,413 @@
       <c r="F1342" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>Amazon Redshift adds support for creating and refreshing Apache Iceberg materialized views</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/redshift-iceberg-materialized-views</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 21:57:18 GMT</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now supports creating and refreshing Apache Iceberg materialized views, enabling efficient data pre-computation and querying across multiple engines.
+2. Outcome (impact):
+Reduces redundant computation, lowers query latency, and simplifies data pipeline orchestration by allowing a single engine to serve multiple consumers.
+3. Where to use (use case):
+Ideal for data teams that need to perform complex joins and aggregations once and share the results across various analytics engines, improving efficiency and consistency.</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>GLM 5.3 by Z.ai is now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-bedrock-glm-5-3/</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 21:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock now supports GLM 5.3 by Z.ai, offering advanced agentic coding and software engineering capabilities with enhanced security.
+2. Outcome (impact):  
+Customers gain access to a powerful, scalable model for long-horizon software tasks, with improved latency and cost efficiency through prompt caching.
+3. Where to use (use case):  
+Ideal for enterprise software development, complex coding tasks, and scenarios requiring long-context understanding and reasoning.</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Service name: Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center now supports network access controls for Identity Store</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-identity-store-network-controls/</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM Identity Center now supports network access controls for Identity Store, enabling restricted access to Identity Store APIs based on network origin.
+2. Outcome (impact):
+Enhanced security for Identity Store by allowing administrators to control API access based on network endpoints or IP ranges, reducing potential exposure to unauthorized access.
+3. Where to use (use case):
+Use this feature to secure Identity Store API access in environments where stringent network controls are required, such as corporate networks or when integrating with external identity providers.</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>AWS Continuum for Penetration Testing now supports continuous penetration testing integrated directly into your CI/CD pipeline</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-continuum-penetration-testing/</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 18:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Continuum for Penetration Testing now integrates continuous security testing directly into CI/CD pipelines, providing real-time findings and remediation guidance.
+2. Outcome (impact):
+Enables faster and more efficient security validation by embedding penetration testing within the deployment workflow, reducing delays and ensuring timely remediation.
+3. Where to use (use case):
+Ideal for development teams that need to integrate security testing into their CI/CD processes to ensure code is secure before deployment.</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>AWS Continuum for Penetration Testing</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>AWS Advanced Ruby Driver Wrapper is generally available</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-ruby-driver-wrapper-available/</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Advanced Ruby Driver Wrapper is now available to reduce failover times for RDS and Aurora PostgreSQL/MySQL databases, supporting multiple authentication mechanisms.
+2. Outcome (impact):
+Improves application availability by decreasing RDS Blue/Green, Aurora Global database switchover, and database failover times.
+3. Where to use (use case):
+Use this driver for Ruby applications connected to Amazon RDS and Amazon Aurora PostgreSQL and MySQL-compatible databases to enhance failover performance and security.</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>AWS Advanced Ruby Driver Wrapper</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>AWS Client VPN now supports device posture assessment</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-client-vpn-device-posture/</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Client VPN now supports device posture assessment, ensuring only compliant devices can access your AWS resources.
+2. Outcome (impact):  
+   Enhances security by verifying device compliance before granting access, reducing the risk of unauthorized access.
+3. Where to use (use case):  
+   Ideal for organizations needing to enforce security policies on devices accessing AWS resources, ensuring they meet specific compliance criteria.</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>AWS Client VPN</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>AWS Batch now supports Amazon EKS access entry authentication</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-batch-access-entries/</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 15:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Batch now supports Amazon EKS access entry authentication, simplifying cluster setup and authentication management.
+2. Outcome (impact):
+   This update enhances security and simplifies the authentication process for AWS Batch compute environments on Amazon EKS.
+3. Where to use (use case):
+   Ideal for organizations managing Kubernetes clusters on Amazon EKS that require streamlined and secure authentication for AWS Batch workloads.</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>AWS Batch</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>AWS Private CA now provides detailed certificate issuance logs</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-private-ca-certificate-issuance-logs/</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Private CA now offers detailed certificate issuance logs via CloudTrail, capturing complete certificate content and issuing CA information for compliance and monitoring.
+2. Outcome (impact):
+   Enhanced visibility and auditing capabilities for certificate issuances, facilitating compliance, inventory management, and failure monitoring.
+3. Where to use (use case):
+   Ideal for organizations requiring detailed tracking of certificate issuances for security audits, inventory management, and migration tracking.</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>AWS Private CA</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>Announcing Amazon Nova 2.5 Sonic with improved reasoning for voice agents</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-nova-2.5-sonic/</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 08:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Nova 2.5 Sonic is a new speech-to-speech model enhancing voice agents with better reasoning, lower latency, and improved task handling.
+2. Outcome (Impact):
+Developers can create more efficient and capable voice agents for customer service, personal assistants, and real-time applications, leading to better user experiences.
+3. Where to Use (Use Case):
+Ideal for customer service interactions, personal AI assistants, and any real-time conversational applications requiring natural and efficient voice interactions.</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Amazon Nova</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>Amazon Q Developer now delivers enhanced visualizations in the AWS Management Console</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-q-developer-enhanced-visualizations-aws-management-console</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 17:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces enhanced visualizations in Amazon Q Developer for faster, more intuitive insights into AWS resources and health.
+2. Outcome (impact):
+   Users can now quickly identify issues and trends through interactive dashboards and charts, improving operational efficiency and decision-making speed.
+3. Where to use (use case):
+   Ideal for monitoring and troubleshooting AWS resources, optimizing performance, and gaining comprehensive insights into account health and resource utilization.</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Amazon Q Developer</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>Amazon EKS Auto Mode now supports advanced compute configuration</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/eks-auto-mode-advanced-compute-config/</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EKS Auto Mode now supports advanced compute configurations, allowing users to tune kubelet settings, sysctls, and hugepages directly in NodeClass resources.
+2. Outcome (impact):
+   Users can now run workloads requiring specific node tuning on EKS Auto Mode, enhancing performance for HPC, database, and latency-sensitive applications without manual infrastructure management.
+3. Where to use (use case):
+   Ideal for CI/CD pipelines needing user namespaces, large clusters requiring higher network and ARP cache limits, and applications sensitive to disk and memory pressure.</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -50272,7 +50679,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03 09:01:07</t>
+          <t>2026-10-06 09:59:37</t>
         </is>
       </c>
     </row>
@@ -50283,7 +50690,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -50293,7 +50700,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3009</v>
+        <v>4311</v>
       </c>
     </row>
     <row r="7">
@@ -50303,7 +50710,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1000</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="8">
@@ -50313,7 +50720,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000214</v>
+        <v>0.000306</v>
       </c>
     </row>
     <row r="9">
@@ -50323,7 +50730,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000284</v>
+        <v>0.000374</v>
       </c>
     </row>
     <row r="10">
@@ -50333,7 +50740,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000498</v>
+        <v>0.00068</v>
       </c>
     </row>
     <row r="11">
@@ -50343,7 +50750,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.083134</v>
+        <v>0.083814</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1353"/>
+  <dimension ref="A1:F1358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -50612,6 +50612,191 @@
         </is>
       </c>
       <c r="F1353" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>AWS Batch now publishes job metrics to Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-batch-job-cloudwatch-metrics/</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Tue, 06 Oct 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Batch now provides job metrics to Amazon CloudWatch, enhancing observability for batch workloads.
+2. Outcome (impact):
+   Improved visibility into job queue health, failure rates, and job durations, enabling better monitoring and troubleshooting.
+3. Where to use (use case):
+   Ideal for managing and monitoring batch processing jobs in environments requiring detailed performance insights.</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>AWS Batch</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>AWS Certificate Manager now supports ACME issuance through AWS PrivateLink</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/AWS-Certificate-Manager-ACME-Privatelink</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Tue, 06 Oct 2026 14:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Certificate Manager now supports ACME certificate issuance over AWS PrivateLink, enabling secure, private network paths for certificate management.
+2. Outcome (impact):  
+   Enhances security by keeping certificate issuance traffic within the AWS network, reducing exposure to the public internet.
+3. Where to use (use case):  
+   Ideal for organizations that require stringent security and compliance standards, such as financial services or healthcare, to manage TLS certificates privately.</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>AWS Certificate Manager</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Hpc8a instances are now available in Asia Pacific (Singapore)</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-ec2-hpc8a-asia-pacific/</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 20:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EC2 Hpc8a instances, powered by 5th Gen AMD EPYC processors, are now available in Asia Pacific (Singapore) with enhanced performance and cost efficiency.
+2. Outcome (impact):  
+Customers can achieve up to 40% higher performance and up to 25% better price performance compared to Hpc7a instances, making compute-intensive workloads more efficient.
+3. Where to use (use case):  
+Ideal for computational fluid dynamics, weather forecasting, finite element analysis, and multiphysics simulations requiring high inter-node communication and performance.</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>AWS Control Tower AFT now supports plan-only customization runs</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-control-tower-aft/</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 19:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Control Tower AFT now allows administrators to preview Terraform changes with plan-only customization runs before applying them.
+2. Outcome (impact):
+Administrators can validate expected outcomes, detect configuration drift, and integrate into CI/CD workflows safely before applying changes.
+3. Where to use (use case):
+Use case for safe pre-rollout validation, drift detection, and integration into CI/CD review workflows in AWS Control Tower environments.</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>AWS Control Tower</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>Amazon EC2 introduces shared tags for Amazon Machine Images</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ec2-ami-shared-tags</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 17:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EC2 now allows AMI owners to share selected tags with accounts that have access to the AMI, simplifying tag management across shared resources.
+2. Outcome (impact):  
+This feature reduces the operational burden of manually replicating tags for shared AMIs, ensuring consistent and automatic tag visibility without affecting the recipient's tag limits.
+3. Where to use (use case):  
+Ideal for organizations that share AMIs across multiple accounts or teams, ensuring consistent tagging and metadata visibility without additional overhead.</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -50679,7 +50864,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:59:37</t>
+          <t>2026-10-07 10:03:59</t>
         </is>
       </c>
     </row>
@@ -50690,7 +50875,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -50700,7 +50885,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4311</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="7">
@@ -50710,7 +50895,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1317</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -50720,7 +50905,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000306</v>
+        <v>0.000116</v>
       </c>
     </row>
     <row r="9">
@@ -50730,7 +50915,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000374</v>
+        <v>0.000168</v>
       </c>
     </row>
     <row r="10">
@@ -50740,7 +50925,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00068</v>
+        <v>0.000284</v>
       </c>
     </row>
     <row r="11">
@@ -50750,7 +50935,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.083814</v>
+        <v>0.08409800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1358"/>
+  <dimension ref="A1:F1362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -50799,6 +50799,154 @@
       <c r="F1358" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>AWS Capabilities by Region now offers availability notifications for individual features and advanced filters</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/awscapabilities-enhancements/</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Capabilities by Region now provides feature-level availability notifications and advanced filters to monitor and compare service features across regions.
+2. Outcome (impact):
+Users can now receive targeted notifications about specific AWS service features becoming available in their regions of interest, and efficiently compare service capabilities across regions.
+3. Where to use (use case):
+This feature is ideal for cloud architects, DevOps engineers, and IT managers who need to plan and deploy services based on regional availability and feature support.</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>AWS Builder Center</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>AWS Config now supports 77 new resource types</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-config-new-resource-types</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Config now supports 77 new resource types, enhancing coverage across services like EC2, S3, and Q Business for better monitoring and compliance.
+2. Outcome (impact):
+This expansion allows for more comprehensive monitoring, assessment, auditing, and remediation of AWS resources, improving overall management and compliance.
+3. Where to use (use case):
+Use AWS Config to monitor and manage the newly supported resource types across all AWS regions where the resources are available, ensuring better governance and compliance.</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>AWS Config</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>Claude Haiku 5.5 is now available on AWS</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/claude-haiku-5-5-aws/</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now offers the efficient and cost-effective Claude Haiku 5.5, designed for high-volume tasks and real-time applications.
+2. Outcome (impact):
+Reduces operational costs by up to 75% compared to its predecessor while enhancing performance and capabilities.
+3. Where to use (use case):
+Ideal for real-time experiences (voice agents, live support) and high-volume tasks (classification, summarization).</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>Claude Haiku 5.5 is now available on AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/claude-haiku-5-5-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS GovCloud (US) now offers the cost-efficient and high-performance Claude Haiku 5.5, designed for real-time applications and high-volume tasks.
+2. Outcome (impact):
+Reduces operational costs by up to 75% compared to previous versions while enhancing capabilities in coding, tool use, and agent interactions.
+3. Where to use (use case):
+Ideal for real-time applications like voice agents, live support, and in-app assistants, as well as high-volume tasks such as classification, summarization, and document field extraction.</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -50864,7 +51012,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:03:59</t>
+          <t>2026-10-08 10:17:30</t>
         </is>
       </c>
     </row>
@@ -50875,7 +51023,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -50885,7 +51033,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1632</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="7">
@@ -50895,7 +51043,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>593</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -50905,7 +51053,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000116</v>
+        <v>0.000126</v>
       </c>
     </row>
     <row r="9">
@@ -50915,7 +51063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000168</v>
+        <v>0.000145</v>
       </c>
     </row>
     <row r="10">
@@ -50925,7 +51073,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000284</v>
+        <v>0.000272</v>
       </c>
     </row>
     <row r="11">
@@ -50935,7 +51083,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08409800000000001</v>
+        <v>0.08437</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1362"/>
+  <dimension ref="A1:F1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -50947,6 +50947,265 @@
       <c r="F1362" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-6.1 Sol now supports Ultrafast mode on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/openai-gpt-sol-ultrafast-amazon/</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 19:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces Ultrafast mode for GPT-6.1 Sol from OpenAI on Amazon Bedrock, enhancing speed for critical applications.
+2. Outcome (impact):
+Faster inference speeds for latency-sensitive applications, improving user experience and efficiency in real-time interactions.
+3. Where to use (use case):
+Ideal for real-time coding assistants, interactive agents, and customer-facing experiences requiring quick, high-quality responses.</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>AWS Cost Explorer, Budgets, and Dashboards now support Amazon Bedrock product attributes</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-bedrock-attributes-in-cost-explorer/</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 18:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Cost Explorer, Budgets, and Dashboards now support Amazon Bedrock product attributes to analyze costs by model, provider, inference type, and feature.
+2. Outcome (impact):
+Finance and platform teams can better understand and manage their Bedrock costs, enabling more informed decisions and cost optimization.
+3. Where to use (use case):
+Track and manage costs for specific models, providers, inference types, and features in applications using Bedrock.</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Cost Explorer, Budgets, Dashboards</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports minor version upgrade prechecks and a new RDS event to help reduce patching downtime</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-rds-oracle-minor-version-upgrade-precheck-new-patching-rds-event/</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Oracle now supports prechecks for minor version upgrades and emits an event when the database is back online, reducing patching downtime.
+2. Outcome (impact):
+Reduces application downtime during minor version upgrades by allowing prechecks and enabling quicker application reconnection.
+3. Where to use (use case):
+Ideal for database administrators managing Oracle databases on Amazon RDS who want to minimize downtime during patching and upgrades.</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall adds wildcard support for container attribute filters</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-network-firewall-container-attributes-wildcard</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Network Firewall now supports wildcard matching in container attribute filters for Amazon EKS and ECS, simplifying rule management for dynamic container environments.
+2. Outcome (impact):
+This enhancement reduces operational overhead and ensures consistent security coverage by allowing the use of wildcard patterns in attribute filters, covering multiple container workloads with a single rule.
+3. Where to use (use case):
+Ideal for dynamic container environments where new application variants are frequently deployed, such as microservices architectures in Amazon EKS and ECS.</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers adds CPU burstability for container fleets</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-gamelift-servers-cpu-burstability</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GameLift Servers now offers CPU burstability for container fleets, allowing developers to optimize resource allocation and performance during peak game server demands.
+2. Outcome (impact):
+   Developers can now balance efficient resource utilization with the ability to handle CPU spikes during critical game moments, improving both performance and cost-efficiency.
+3. Where to use (use case):
+   Ideal for game developers managing real-time multiplayer games that experience variable CPU loads, such as during physics calculations, AI processing, or collision detection.</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Amazon GameLift</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8gb instances now generally available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-ec2-c8gb/</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 18:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8gb instances, powered by AWS Graviton4 processors, are now available in multiple regions, offering improved compute and EBS performance.
+2. Outcome (impact):
+   Users can leverage up to 30% better compute performance and higher EBS bandwidth (up to 300 Gbps) and IOPS (up to 1600K) for high-performance workloads, optimizing cost and scalability.
+3. Where to use (use case):
+   Ideal for high-performance file systems, tightly coupled clusters, and workloads requiring enhanced block storage performance and networking capabilities.</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service introduces validation advisory for domain configuration changes</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/opensearch-validation-advisory/</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 09:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service now offers validation advisories for domain configuration changes, providing Critical and Warning alerts to help manage risky changes without blocking deployments.
+2. Outcome (impact):
+   This feature enables users to identify and address potential issues in domain configurations proactively, reducing the risk of operational disruptions while maintaining flexibility in applying changes.
+3. Where to use (use case):
+   This is particularly useful for managing complex OpenSearch and Elasticsearch clusters where configuration changes can have significant impacts on performance and stability.</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -51012,7 +51271,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 10:17:30</t>
+          <t>2026-10-09 10:18:31</t>
         </is>
       </c>
     </row>
@@ -51023,7 +51282,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -51033,7 +51292,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1781</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="7">
@@ -51043,7 +51302,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>512</v>
+        <v>876</v>
       </c>
     </row>
     <row r="8">
@@ -51053,7 +51312,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000126</v>
+        <v>0.000187</v>
       </c>
     </row>
     <row r="9">
@@ -51063,7 +51322,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000145</v>
+        <v>0.000249</v>
       </c>
     </row>
     <row r="10">
@@ -51073,7 +51332,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000272</v>
+        <v>0.000436</v>
       </c>
     </row>
     <row r="11">
@@ -51083,7 +51342,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08437</v>
+        <v>0.08480600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1369"/>
+  <dimension ref="A1:F1381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -51206,6 +51206,450 @@
       <c r="F1369" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>AWS Security Hub now exports findings to S3 in CSV or JSON format</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/security-hub-exports-s3-csv-json/</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Security Hub now allows exporting security findings to S3 in CSV or JSON format for compliance and auditing.
+2. Outcome (impact):  
+Security teams can easily export findings for compliance reporting and audit evidence without custom pipelines.
+3. Where to use (use case):  
+Use this feature for compliance reporting, audit evidence, and integrating findings into other systems.</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8gd instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-ec2-r8gd-thf/</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 19:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 R8gd instances, powered by AWS Graviton4 processors, are now available in the AWS European Sovereign Cloud (Germany) region, offering high-speed local storage and enhanced performance.
+2. Outcome (impact):
+Customers can now leverage high-performance, low-latency local storage with improved network capabilities in the Germany region, optimizing workloads requiring significant local storage and compute power.
+3. Where to use (use case):
+Ideal for data-intensive applications, such as big data analytics, high-performance computing (HPC), and machine learning workloads that benefit from fast, local NVMe-based SSD storage.</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8g instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-ec2-r8g-instances-thf/</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 19:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon EC2 R8g instances, powered by AWS Graviton4 processors, are now available in the AWS European Sovereign Cloud (Germany) region, offering up to 30% better performance.
+2. Outcome (impact):  
+   Enhanced performance and energy efficiency for memory-intensive workloads, with up to 30% faster performance for various applications compared to previous generations.
+3. Where to use (use case):  
+   Ideal for databases, in-memory caches, real-time big data analytics, web applications, and large Java applications.</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock now supports reasoning summaries for OpenAI models</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-bedrock-reasoning-summaries-openai/</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 17:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>1. Short Summary  
+   Amazon Bedrock now offers reasoning summaries for OpenAI models to enhance understanding of model reasoning.
+2. Outcome (impact)  
+   Developers can better evaluate, debug, and explain model responses, improving application reliability and user trust.
+3. Where to use (use case)  
+   Ideal for applications requiring complex task analysis, such as coding assistance, data analysis, and multi-step problem solving.</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>Anthropic Claude Sonnet 5.5 and Claude Opus 5.5 are now available on Kiro in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/kiro-claude-5-5-aws-govcloud-us/</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 17:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Anthropic's latest models, Claude Sonnet 5.5 and Opus 5.5, are now accessible on Kiro in AWS GovCloud (US), offering enhanced performance and efficiency.
+2. Outcome (impact):
+   These new models provide significant improvements in task efficiency and speed, reducing tool calls and tokens while maintaining high performance for coding and knowledge work.
+3. Where to use (use case):
+   Ideal for long-running agentic coding tasks, real-time collaboration, and scenarios requiring a balance between maximum capability and higher throughput.</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>Kiro</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now provides automated checks to improve performance evaluation forms</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-connect-customer-automated-checks-evaluation-forms/</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now offers automated checks to enhance the accuracy of AI-filled performance evaluation forms, providing managers with context-specific suggestions.
+2. Outcome (impact):
+   Managers can ensure fairer and more accurate scoring of both human and AI agents by quickly refining their evaluation forms with AI-driven recommendations.
+3. Where to use (use case):
+   Ideal for contact center managers who need to create and maintain performance evaluation forms to assess agent performance effectively.</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors metadata pre-filtering is now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/s3-vectors-metadata-pre-filtering-in-govcloud-regions/</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Vectors now offers metadata pre-filtering in AWS GovCloud (US) Regions, enhancing retrieval-augmented generation and semantic search applications.
+2. Outcome (impact):
+Improves the efficiency and relevance of vector search queries by up to 5x when filters are selective, leading to more accurate and complete results for applications.
+3. Where to use (use case):
+Ideal for retrieval-augmented generation (RAG), agentic, and semantic-search applications requiring precise and efficient vector retrieval from Amazon S3.</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>AWS Lambda supports OAuth authentication for self-managed Apache Kafka event sources</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-Lambda-supports-oauth-kafka-esm/</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Lambda now supports OAuth authentication for self-managed Apache Kafka event sources, enhancing security for serverless Kafka consumers.
+2. Outcome (impact):  
+Customers can now authenticate their Lambda Kafka consumers using OAuth, meeting stringent security and compliance requirements for regulated industries.
+3. Where to use (use case):  
+Ideal for event-driven workloads such as payment processing, fraud detection, and real-time data pipelines.</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports brand templates for on-brand presentations and documents</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-quick-brand-templates-on-brand-presentations-documents/</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick now supports brand templates to ensure presentations and documents align with your company's visual identity.
+2. Outcome (impact):
+   Ensures consistent brand representation across all documents and presentations, reducing errors and saving time for brand managers.
+3. Where to use (use case):
+   Ideal for marketing, communications, and brand management teams to maintain a cohesive visual identity in all digital outputs.</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports custom Tooling blueprints</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/sagemaker-custom-tooling-blueprints/</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now allows domain administrators to create custom project environments using their own AWS CloudFormation templates.
+2. Outcome (impact):
+Administrators can tailor project environments to meet specific organizational requirements, ensuring compliance with company standards and enhancing project efficiency.
+3. Where to use (use case):
+This feature is ideal for organizations that need to standardize project environments across multiple teams and regions, ensuring consistent IAM roles, permissions, and resource configurations.</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>TwelveLabs Pegasus 1.5 model now available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/twelve-labs-pegasus-1-5-aws/</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 05:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock now offers TwelveLabs Pegasus 1.5, a video-to-text model that generates time-coded metadata from video, enabling efficient video search and querying.
+2. Outcome (Impact):  
+Pegasus 1.5 simplifies video content management by automatically labeling and timestamping key moments in videos, enhancing searchability and accessibility.
+3. Where to Use (Use Case):  
+Ideal for applications requiring video indexing, such as media libraries, sports analysis, content moderation, and brand monitoring.</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty RDS Protection now detects data exfiltration and destruction in Aurora and RDS databases</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/guardduty-rds-data-exfiltration/</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GuardDuty now detects data exfiltration and destruction in Aurora and RDS databases using ML-based anomaly detection.
+2. Outcome (impact):
+   Enhanced security for Amazon Aurora and RDS databases by identifying and mitigating data exfiltration and destruction attacks without additional infrastructure.
+3. Where to use (use case):
+   Protecting sensitive data in Amazon Aurora and RDS databases from malicious activities such as data theft and destruction.</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -51271,7 +51715,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 10:18:31</t>
+          <t>2026-10-10 09:38:38</t>
         </is>
       </c>
     </row>
@@ -51282,7 +51726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -51292,7 +51736,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2637</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="7">
@@ -51302,7 +51746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>876</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="8">
@@ -51312,7 +51756,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000187</v>
+        <v>0.000316</v>
       </c>
     </row>
     <row r="9">
@@ -51322,7 +51766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000249</v>
+        <v>0.000418</v>
       </c>
     </row>
     <row r="10">
@@ -51332,7 +51776,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000436</v>
+        <v>0.000734</v>
       </c>
     </row>
     <row r="11">
@@ -51342,7 +51786,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08480600000000001</v>
+        <v>0.08554</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1381"/>
+  <dimension ref="A1:F1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -51650,6 +51650,450 @@
       <c r="F1381" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront now supports AWS Lambda Web Functions as an origin</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/cloudfront-lambda-web-functions-origin/</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 23:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudFront now supports AWS Lambda Web Functions as an origin, enabling faster, more secure web application delivery globally.
+2. Outcome (impact):
+   This integration allows for TLS termination at the edge, caching, custom domains, and enhanced security through Origin Access Control and AWS WAF, without requiring changes to application code.
+3. Where to use (use case):
+   Ideal for delivering web applications built on AWS Lambda Web Functions with improved performance, lower latency, and robust security.</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G7 instances now available in Europe (Frankfurt) and Europe (Stockholm) Regions</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-g7-european-regions/</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 22:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 G7 instances, powered by RTX PRO 4500 GPUs, are now available in Europe (Frankfurt and Stockholm) with enhanced AI and graphics performance.
+2. Outcome (Impact):
+G7 instances offer up to 4.6x AI inference and 2.1x graphics performance compared to G6 instances, boosting capabilities for AI, graphics, and data analytics workloads.
+3. Where to Use (Use Case):
+Ideal for AI model deployment, video/image analysis, speech recognition, real-time graphics rendering, game streaming, video transcoding, spatial computing, and data analytics.</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now prefills step-by-step guides for after contact work</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/connect-customer-prefills-guides-acw</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 22:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer now automates step-by-step guides post-contact using extracted conversation data.
+2. Outcome (impact):  
+Reduces agent time spent on data entry and minimizes errors, enhancing efficiency and accuracy.
+3. Where to use (use case):  
+Ideal for contact centers needing to streamline post-contact workflows, such as insurance claims processing.</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>AWS Lambda announces Lambda Web Functions</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-lambda-web-functions/</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 19:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Lambda introduces Lambda Web Functions, enabling developers to handle HTTP requests directly using familiar frameworks like Express or Hono, with billing based on active CPU usage.
+2. Outcome (impact):  
+Lambda Web Functions reduce cold starts significantly, offer low-latency responses, and allow developers to use preferred frameworks without additional configuration, enhancing developer experience and efficiency.
+3. Where to use (use case):  
+Ideal for AI inference endpoints, server-side rendered web apps, streaming APIs, microservices, and webhooks, providing a serverless solution for handling direct HTTP requests.</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>Announcing consumption-based pricing for short-term memory in Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/agentcore-memory-consumption-based-pricing</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore now offers consumption-based pricing for short-term memory, charging based on data ingestion, retrieval, and storage.
+2. Outcome (impact):
+Developers will pay proportionally to their usage, potentially reducing costs, especially for small-payload use cases.
+3. Where to use (use case):
+Ideal for building agents that handle frequent, small data events, such as customer service chatbots or interactive applications.</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family supports custom ports for public SFTP servers</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/transfer-family-custom-ports-sftp/</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Transfer Family now allows configuring custom ports for public SFTP servers and selecting communication modes per port.
+2. Outcome (impact):
+   This update enables businesses to use specific port numbers required by their network or clients and choose between client-first or server-first communication modes, enhancing compatibility and security.
+3. Where to use (use case):
+   Ideal for organizations needing to support multiple SFTP clients with different port requirements or those looking to minimize unwanted connection attempts by using non-standard ports.</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>Amazon S3 Express One Zone is now available in 4 additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/s3-express-one-zone-4-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Express One Zone is now available in 4 new regions, offering high-performance, single-digit millisecond data access.
+2. Outcome (impact):
+This expansion enhances data access speed by up to 10x and reduces request costs by up to 80% for latency-sensitive applications.
+3. Where to use (use case):
+Ideal for machine learning training, interactive analytics, and key-value caching in AI search engines.</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Amazon S3 Express One Zone</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager adds managed external secrets support for Databricks and Twilio</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/secrets-manager-managed-external-secrets-databricks-twilio/</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Secrets Manager now supports automatic credential rotation for Databricks and Twilio, simplifying the management of long-lived credentials.
+2. Outcome (impact):
+This update enhances security by automatically rotating credentials, reducing the risk of credential exposure and simplifying the management of secrets for data pipelines and messaging applications.
+3. Where to use (use case):
+Use this feature to securely manage and automatically rotate credentials for Databricks personal access tokens and Twilio API keys and Auth Tokens in your data pipelines, CI/CD workflows, and messaging applications.</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache for Valkey introduces ElastiCache Insights</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-elasticache-valkey-elasticache-insights/</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ElastiCache for Valkey now offers ElastiCache Insights, a unified dashboard in CloudWatch for monitoring cluster health and performance metrics.
+2. Outcome (impact):
+   Enhanced visibility into cache cluster performance, enabling proactive monitoring and troubleshooting of node-based Valkey clusters.
+3. Where to use (use case):
+   Ideal for managing and monitoring Valkey clusters to ensure optimal performance and to quickly detect and resolve issues.</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>Amazon EMR now supports native data quality checks in Apache Spark jobs</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-emr-data-quality-spark/</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EMR now supports native data quality checks within Apache Spark jobs, enabling data engineers to validate data inline without additional infrastructure.
+2. Outcome (impact):
+   This feature allows teams to catch data quality issues early in the pipeline, ensuring better data integrity and reducing the risk of bad data reaching downstream systems.
+3. Where to use (use case):
+   Ideal for data engineering teams working with Apache Spark jobs on Amazon EMR, ensuring data quality across various deployment modes like EC2, EKS, and Serverless.</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service now supports index-level encryption</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/opensearch-index-level-encryption</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 02:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Service now supports index-level encryption, allowing individual indices to be encrypted with separate AWS KMS keys for enhanced data protection.
+2. Outcome (impact):
+This feature enables better data security and compliance by allowing different indices to be encrypted with different keys, suitable for multi-tenant applications.
+3. Where to use (use case):
+Ideal for multi-tenant applications where different tenants' data need to be encrypted with separate keys for ownership or sensitivity.</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>AWS now lets customers sign up for AWS and pay invoices using ACH direct debit</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-sign-up-invoices-ach-direct-debit/</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now allows U.S. customers to sign up and pay using ACH direct debit from their bank accounts, offering a secure alternative to credit/debit cards.
+2. Outcome (impact):
+This update simplifies the sign-up process and provides a convenient payment method for U.S. customers, potentially increasing user adoption and satisfaction.
+3. Where to use (use case):
+Ideal for businesses and individuals who prefer not to use credit/debit cards for online payments, ensuring a smoother onboarding and billing experience.</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>AWS Billing and Cost Management</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -51715,7 +52159,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10 09:38:38</t>
+          <t>2026-10-13 10:21:16</t>
         </is>
       </c>
     </row>
@@ -51736,7 +52180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4445</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="7">
@@ -51746,7 +52190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1473</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="8">
@@ -51756,7 +52200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000316</v>
+        <v>0.00033</v>
       </c>
     </row>
     <row r="9">
@@ -51766,7 +52210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000418</v>
+        <v>0.00043</v>
       </c>
     </row>
     <row r="10">
@@ -51776,7 +52220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000734</v>
+        <v>0.000759</v>
       </c>
     </row>
     <row r="11">
@@ -51786,7 +52230,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08554</v>
+        <v>0.086299</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1393"/>
+  <dimension ref="A1:F1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -52094,6 +52094,376 @@
       <c r="F1393" t="inlineStr">
         <is>
           <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>AWS Security Hub now supports resource criticality for prioritization</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/security-hub-resource-criticality/</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 01:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Security Hub now prioritizes resource exposure by incorporating criticality, aiding central security teams in focusing on the most critical business resources.
+2. Outcome (impact):
+   Security teams can more effectively prioritize remediation efforts by identifying and addressing vulnerabilities that threaten the most critical resources, thereby enhancing overall security posture.
+3. Where to use (use case):
+   This feature is ideal for central security teams managing multiple AWS accounts and resources, allowing them to efficiently prioritize security tasks based on resource importance.</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>Amazon ECS adds LiveTaskCount and removes the charge for RunningTaskCount metric</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ecs-service-metrics/</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS introduces the LiveTaskCount metric for free, while removing charges for the RunningTaskCount metric.
+2. Outcome (impact):
+Customers benefit from a more comprehensive view of running tasks with LiveTaskCount and no additional costs for RunningTaskCount.
+3. Where to use (use case):
+Ideal for autoscaling policies and capacity planning requiring a complete view of active tasks.</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>AWS Agent Registry now supports custom metadata for registry records</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-agent-registry-custom-metadata-registry-records</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Agent Registry now supports custom metadata to enhance resource governance and discovery.
+2. Outcome (impact):  
+Organizations can now manage and discover resources more effectively by adding structured metadata to registry records.
+3. Where to use (use case):  
+Useful for managing and governing a growing number of agents, servers, skills, and resources within an organization.</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>AWS Agent Registry</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>Amazon DCV releases version 2026.0 with RHEL 10 support and new clients</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-dcv-2026-0/</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 19:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon DCV 2026.0 introduces support for RHEL 10, Rocky Linux 10, CentOS 10, and Ubuntu 26.04, along with a new macOS client and enhanced clients for Windows and Linux.
+2. Outcome (impact):
+This release enhances the flexibility and security of remote desktop access, providing better compatibility with modern Linux distributions and improved client experiences with new features and performance optimizations.
+3. Where to use (use case):
+Ideal for IT administrators and developers needing secure, high-performance remote access to various operating systems, particularly in environments requiring support for the latest Linux distributions and macOS.</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>Amazon DCV</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now helps users find their accessible resources in the Deadline Cloud monitor</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/deadline-cloud/resources</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 18:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Deadline Cloud now enables users with limited access to find and access their specific resources directly from the Deadline Cloud monitor.
+2. Outcome (impact):
+   Users with access to specific queues, fleets, or jobs can now directly locate and manage their resources without needing additional administrative assistance, improving efficiency and reducing coordination overhead.
+3. Where to use (use case):
+   Ideal for teams running compute-intensive workloads in visual effects, animation, product design, simulation, and gaming where different team members have varying levels of access to resources.</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>Amazon Location Service launches an interactive API Playground featuring Places, Routes and Maps APIs</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-location-service-api-playground</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 18:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Location Service introduces an interactive API Playground for testing Places, Routes, and Maps APIs without coding, available in multiple regions.
+2. Outcome (impact):
+Developers can efficiently test and visualize API functionalities, streamline application development, and reduce setup time for SDKs and test scripts.
+3. Where to use (use case):
+Use cases include validating delivery addresses, planning multi-stop routes, visualizing service areas, and embedding maps in applications.</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Amazon Location Service</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>Bring deep SageMaker AI expertise to your coding agent with the AWS AI/ML skill in the Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/bring-sagemaker-ai-expertise-to-your-coding-agent/</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces a new AI/ML skill in the Agent Toolkit for AWS, enabling coding agents to manage Amazon SageMaker AI tasks within a unified natural-language workflow.
+2. Outcome (impact):
+   This integration enhances productivity by allowing seamless model training, optimization, and deployment on SageMaker, alongside other AWS services, all through a single interface.
+3. Where to use (use case):
+   Ideal for data scientists and ML engineers who need to streamline their workflows across AWS services, particularly within SageMaker Studio for model development and deployment.</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>AWS DataSync Enhanced mode now supports FSx for OpenZFS, NFS 4.2, and object metadata controls</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/datasync-enhanced-openzfs-nfs42-metadata/</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS DataSync Enhanced mode now supports FSx for OpenZFS, NFS 4.2, and object metadata controls for more flexible data transfers.
+2. Outcome (impact):
+Customers can now transfer data to/from FSx for OpenZFS using Enhanced mode, leverage NFS 4.2 for compatibility with modern NFS servers, and manage object metadata during transfers.
+3. Where to use (use case):
+Ideal for migrating data to/from FSx for OpenZFS, transferring data from NFS 4.2 servers, and maintaining metadata integrity during object storage transfers.</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>AWS DataSync</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 now supports registrations, transfers, and renewals for Premium Domains</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/route-53-premium-domains/</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Route 53 now supports premium domain registrations, transfers, and renewals, allowing unified management of all domains.
+2. Outcome (impact):
+Customers can now manage premium and standard domains in one place, simplifying domain management and reducing fragmentation across multiple registrars.
+3. Where to use (use case):
+Ideal for businesses and individuals seeking to consolidate domain management, especially those with premium domains, to streamline operations and improve oversight.</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>Route 53</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports the latest CU for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-supports-latest-cu-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for SQL Server now supports the latest Cumulative Update (CU8) for Microsoft SQL Server, enhancing performance and security.
+2. Outcome (impact):
+Users can benefit from the latest features, performance improvements, and security fixes provided by Microsoft SQL Server CU8.
+3. Where to use (use case):
+Ideal for enterprise applications requiring the latest SQL Server updates to ensure optimal performance, security, and compliance.</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -52159,7 +52529,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13 10:21:16</t>
+          <t>2026-10-14 08:33:19</t>
         </is>
       </c>
     </row>
@@ -52170,7 +52540,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -52180,7 +52550,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4645</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="7">
@@ -52190,7 +52560,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1513</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="8">
@@ -52200,7 +52570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00033</v>
+        <v>0.000254</v>
       </c>
     </row>
     <row r="9">
@@ -52210,7 +52580,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00043</v>
+        <v>0.000352</v>
       </c>
     </row>
     <row r="10">
@@ -52220,7 +52590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000759</v>
+        <v>0.000606</v>
       </c>
     </row>
     <row r="11">
@@ -52230,7 +52600,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.086299</v>
+        <v>0.086905</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1403"/>
+  <dimension ref="A1:F1418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -52464,6 +52464,563 @@
       <c r="F1403" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch announces log routing and chained log parsers</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/cloudwatch-pipelines-log-routing/</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 22:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch introduces conditional log routing and chained parsers to enhance log data transformation and routing within pipelines.
+2. Outcome (impact):
+   This update allows users to better manage and organize log data by separating events based on conditions and applying multiple parsers in sequence, improving log management efficiency and accuracy.
+3. Where to use (use case):
+   Ideal for environments with diverse log formats and complex routing requirements, such as large-scale applications with mixed telemetry data needing precise log separation and retention policies.</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio simplifies getting started for new AI/ML builders with social sign-in</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/sagemaker-studio-social-sign-in/</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon SageMaker Studio now allows new users to sign in with Google, GitHub, or Apple credentials, providing immediate access to a configured environment without needing to set up an AWS account or provide a credit card.
+2. Outcome (impact):  
+   Simplifies the onboarding process for new AI/ML builders, reducing barriers to entry and enabling faster experimentation and deployment of machine learning models.
+3. Where to use (use case):  
+   Ideal for new users and teams looking to quickly start experimenting with machine learning models on AWS without the complexities of traditional AWS account setup.</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>ARC Region switch adds four new capabilities</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/region-switch-target-health-ssm-lambda/</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 17:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS ARC Region switch introduces four new capabilities to streamline multi-Region application failover, ensuring faster recovery during Regional impairments.
+2. Outcome (impact):
+   Enhanced reliability and efficiency in multi-Region application failover, reducing recovery time and minimizing service disruptions.
+3. Where to use (use case):
+   Ideal for organizations running critical applications across multiple AWS Regions that require orchestrated failover strategies to maintain high availability.</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>Amazon Application Recovery Controller (ARC)</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>AWS License Manager now supports license type conversions for Ubuntu Pro purchased through AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-license-manager-conversions-ubuntu-pro-marketplace/</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 17:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS License Manager now supports converting EC2 Ubuntu LTS instances to Ubuntu Pro via AWS Marketplace, enhancing security and compliance.
+2. Outcome (impact):  
+   Customers can upgrade their Ubuntu instances to Ubuntu Pro without rebuilding or migrating, ensuring extended security patches and kernel live patching.
+3. Where to use (use case):  
+   Ideal for organizations needing long-term security and compliance for their Ubuntu-based EC2 instances.</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>AWS License Manager</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics introduces resource fallback order for Nextflow workflows</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-healthomics-resource-fallback-for-Nextflow/</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now offers a resource fallback directive for Nextflow workflows, allowing users to specify preferred accelerator types and fallback options to optimize task execution.
+2. Outcome (impact):
+This feature reduces the time spent diagnosing and resubmitting runs due to accelerator constraints, ensuring continuous operation of bioinformatics workflows.
+3. Where to use (use case):
+Ideal for researchers and bioinformaticians managing large-scale genomic data analysis who need reliable and efficient task execution across various AWS regions.</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>AWS Backup now supports Amazon FSx file systems in the Asia Pacific (New Zealand) Region</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-backup-fsx-asia-pacific-new-zealand/</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Backup now supports Amazon FSx file systems in the Asia Pacific (New Zealand) Region, enabling centralized data protection.
+2. Outcome (impact):
+Centralizes data protection for FSx file systems, ensuring business continuity, disaster recovery, and compliance from a single service.
+3. Where to use (use case):
+Ideal for organizations needing to protect FSx file systems in the New Zealand region, ensuring data integrity and compliance.</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>Announcing Blockchain Snapshots on AWS for node bootstrapping</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/blockchain-snapshots-node-bootstrapping/</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces Blockchain Snapshots on AWS, offering pre-synced Ethereum and Solana blockchain data on Amazon S3 to expedite node setup.
+2. Outcome (impact):  
+Reduces node bootstrap time significantly, enhances reliability for RPC fleets, and simplifies node recovery and re-syncing.
+3. Where to use (use case):  
+Ideal for blockchain node operators looking to quickly deploy, recover, or re-sync nodes on AWS, particularly in high-demand scenarios.</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family console supports SVG logos and ICO favicons for web apps</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/transfer-family-svg-ico-favicons/</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transfer Family now supports SVG logos and ICO favicons for web apps, with increased upload limits to 2 MB.
+2. Outcome (impact):  
+This update provides greater flexibility in using existing branding assets for web app customization, enhancing user experience and brand consistency.
+3. Where to use (use case):  
+Use this feature to customize your web applications with your company's branding, ensuring a consistent look and feel across your web interfaces.</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family now supports AWS Secrets Manager storage for SFTP server host keys</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/transfer-family-secrets-host-keys/</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transfer Family now supports storing SFTP server host keys in AWS Secrets Manager, enhancing control over server identity and simplifying migrations and failover.
+2. Outcome (impact):  
+This update allows users to manage their SFTP server host keys more securely and flexibly, enabling easier server migrations and failover without requiring clients to trust new host keys.
+3. Where to use (use case):  
+Use this feature for secure SFTP server management, simplifying server migrations and failover processes, and ensuring consistent server identity across AWS Regions.</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>Amazon RDS Proxy now supports SQL Server 2022</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/rds-proxy-supports-sqlserver-2022</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS Proxy now supports SQL Server 2022, enhancing connection pooling and failover efficiency for SQL Server databases.
+2. Outcome (impact):
+Improves database efficiency, application scalability, and reduces failover times by up to 83% for SQL Server Multi-AZ databases.
+3. Where to use (use case):
+Ideal for applications requiring high availability and efficient connection management for SQL Server databases.</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Amazon RDS Proxy</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>Amazon S3 is now available on the Vercel Marketplace and v0 by Vercel</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-s3-vercel-marketplace-v0</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon S3 is now available on the Vercel Marketplace, enabling developers to easily provision and connect S3 resources directly from their development environment.
+2. Outcome (impact):
+   This integration streamlines the process of setting up S3 resources, reducing the time and complexity involved, and providing immediate access to S3's durability, scalability, and performance.
+3. Where to use (use case):
+   Ideal for web and AI application development, data storage, analytics, and vector storage needs within the Vercel platform.</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>AWS Lambda durable functions increases durable operation and checkpoint payload limits</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-lambda-durable-gen-limit-increase/</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Lambda durable functions now support up to 30,000 operations per execution and 1 MB checkpoint payloads, enhancing resilience and complexity in multi-step applications.
+2. Outcome (impact):  
+Developers can build more complex, long-running workflows with increased operation limits and larger checkpoint payloads, improving the efficiency and capability of multi-step applications.
+3. Where to use (use case):  
+Ideal for building resilient, long-running applications, AI workflows, and complex multi-step processes that require extensive iteration, polling, or state management.</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8id instances now available in Asia Pacific (Malaysia) and Asia Pacific (Sydney)</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ec2-m8id-asia-pacific-malaysia-sydney/</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 M8id instances with enhanced compute, memory, and local storage are now available in Asia Pacific (Malaysia) and Asia Pacific (Sydney), ideal for data logging, media processing, and real-time analytics.
+2. Outcome (Impact):
+Customers can achieve up to 43% higher compute performance and 30% faster query results for I/O intensive workloads, with greater flexibility in bandwidth allocation.
+3. Where to Use (Use Case):
+Ideal for data logging, media processing, medium-sized data stores, and I/O intensive real-time data analytics.</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C9g, C9gd, M9g, and M9gd instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ec2-c9g-m9g-instances-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C9g, C9gd, M9g, and M9gd instances, powered by AWS Graviton5 processors, are now available in new regions with enhanced performance and security.
+2. Outcome (impact):
+These instances offer up to 25% better compute performance and up to 35% faster performance for databases, web applications, and machine learning, with the new Nitro Isolation Engine ensuring enhanced security.
+3. Where to use (use case):
+- C9g/C9gd: High-performance computing, batch processing, gaming, video encoding, scientific modeling, real-time analytics, CPU-based ML inference, ad serving.
+- M9g/M9gd: General-purpose workloads, application servers, microservices, gaming, caching, containers, real-time reasoning, code generation, multi-step orchestration.</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8gd and M8gd instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ec2-c8gd-m8gd-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C8gd and M8gd instances with high local storage and enhanced performance are now available in more regions.
+2. Outcome (impact):
+Users can now deploy high-performance, I/O intensive applications in additional regions with improved efficiency and cost-effectiveness.
+3. Where to use (use case):
+- C8gd: High-performance web servers, batch processing, distributed analytics, ad serving, video encoding, gaming servers.
+- M8gd: Application servers, microservices, enterprise applications, small to medium databases.</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -52529,7 +53086,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 08:33:19</t>
+          <t>2026-10-15 08:08:48</t>
         </is>
       </c>
     </row>
@@ -52540,7 +53097,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -52550,7 +53107,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3580</v>
+        <v>5994</v>
       </c>
     </row>
     <row r="7">
@@ -52560,7 +53117,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1239</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="8">
@@ -52570,7 +53127,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000254</v>
+        <v>0.000426</v>
       </c>
     </row>
     <row r="9">
@@ -52580,7 +53137,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000352</v>
+        <v>0.000564</v>
       </c>
     </row>
     <row r="10">
@@ -52590,7 +53147,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000606</v>
+        <v>0.00099</v>
       </c>
     </row>
     <row r="11">
@@ -52600,7 +53157,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.086905</v>
+        <v>0.087895</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1418"/>
+  <dimension ref="A1:F1440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -53021,6 +53021,819 @@
       <c r="F1418" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>Web Search on Amazon Bedrock AgentCore expands to AWS GovCloud and 3 Regions</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-bedrock-agentcore/</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 20:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Web Search on Amazon Bedrock AgentCore is now available in four new regions, enhancing AI agents' access to up-to-date web information with lower latency.
+2. Outcome (impact):
+Customers can now deploy AI agents with improved accuracy and timeliness for tasks like research and summarization, especially for government workloads in AWS GovCloud.
+3. Where to use (use case):
+Ideal for applications requiring real-time web data retrieval, such as customer support, research tools, and content summarization.</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio simplifies getting started for new AI/ML builders with new sign-in options</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/sagemaker-studio-new-sign-in-options/</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 20:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Studio now allows new users to sign in with Google, GitHub, or Apple credentials, providing immediate access to a configured environment without needing to set up an AWS account.
+2. Outcome (impact):
+   Simplifies the onboarding process for new AI/ML builders, reducing the time and complexity required to start using SageMaker Studio, and enabling users to begin working with foundation models more quickly.
+3. Where to use (use case):
+   Ideal for new users who want to quickly start experimenting with machine learning models on SageMaker without the hassle of traditional AWS account setups.</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>Amazon EC2 T8i instances are now available in South America (São Paulo)</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ec2-t8i-instances-south-america/</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched T8i instances in South America (São Paulo), offering better price performance and enhanced capabilities over previous T3 instances.
+2. Outcome (impact):
+Customers can achieve up to 30% better price performance and significant improvements in compute, network, and EBS bandwidth, making T8i instances more cost-effective and powerful.
+3. Where to use (use case):
+Ideal for workloads requiring low to moderate CPU utilization, such as data processing, login gateways, small databases, batch processing, CI/CD pipelines, microservices, and low traffic websites.</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB Streams now supports timestamp-based stream processing</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-dynamodb-streams-timestamp-processing</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DynamoDB Streams now supports timestamp-based stream processing, allowing users to start reading records from a specific point in time.
+2. Outcome (impact):
+   This feature enables more efficient data processing by avoiding reprocessing of entire streams and helps in scenarios like recovery after interruptions, debugging, and auditing.
+3. Where to use (use case):
+   Useful for recovery after interruptions, data replay for debugging and auditing, skipping backlogs, and synchronizing after a restore.</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>AWS Lambda Durable Execution SDK for Go is now generally available</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-lambda-durable-go-sdk-support/</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 18:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has released the general availability of the Lambda Durable Execution SDK for Go, enabling developers to build resilient, long-running workflows using Lambda durable functions.
+2. Outcome (impact):  
+Developers can now create complex, multi-step applications directly in Go without needing to implement custom progress tracking, enhancing resilience and efficiency in long-running processes.
+3. Where to use (use case):  
+This SDK is ideal for infrastructure automation, deployment rollouts with approval gates, and AI model pipelines that require human review, all within Go applications.</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>Muse Spark Open model now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/muse-spark-open-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Meta's Muse Spark Open model is now available on Amazon SageMaker JumpStart, enhancing coding workflows with multi-step reasoning and tool calling.
+2. Outcome (impact):  
+   AWS customers can leverage a powerful, coding-optimized model for agentic coding, improving efficiency in software engineering tasks.
+3. Where to use (use case):  
+   Suitable for long-running coding agents, multi-file refactors, and complex debugging sessions in enterprise software engineering.</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports shared VPCs</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/omics-workflows-shared-vpcs/</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 17:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now supports shared VPCs, allowing workflows to access resources in VPCs managed by other accounts via AWS RAM.
+2. Outcome (impact):
+This feature centralizes networking administration, reduces infrastructure overhead, and simplifies network management for organizations with centralized networking.
+3. Where to use (use case):
+Ideal for healthcare and life sciences organizations that need to run bioinformatics workflows across multiple accounts while maintaining centralized network control.</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>Amazon Time Sync Service adds support for microsecond-accurate time on 135 additional EC2 instance types in all commercial regions</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/time-sync-additional-instances-all-regions</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 17:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Time Sync Service now offers microsecond-accurate time on 135 additional EC2 instance types across 12 families, enhancing precision for various applications.
+2. Outcome (impact):
+This update allows developers to order application events more precisely, measure network latency accurately, and boost distributed application transaction speeds.
+3. Where to use (use case):
+Ideal for applications requiring high-precision timing, such as financial trading systems, high-frequency trading, and real-time analytics.</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>Amazon Time Sync Service</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>AWS Transform for full-stack Windows modernization now supports Aurora PostgreSQL cross-region deployment in 7 more Regions</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-transform-full-stack-aurora-cross-region</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now supports cross-region deployment of Aurora PostgreSQL in 7 additional regions, enhancing data residency and disaster recovery options.
+2. Outcome (impact):  
+Customers gain more flexibility in deploying modernized databases across regions, improving data management and disaster recovery strategies.
+3. Where to use (use case):  
+Ideal for enterprises needing to comply with data residency laws, reduce latency, or enhance disaster recovery plans through cross-region database deployment.</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>Service Name: AWS Transform for full-stack Windows modernization  
+Category: Database</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>Amazon MSK Connect and AWS Glue Schema Registry are now available in the AWS European Sovereign Cloud (Germany) region</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-msk-connect-aws-gsr-additional-aws-regions</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 16:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MSK Connect and AWS Glue Schema Registry are now available in the AWS European Sovereign Cloud (Germany) region, enhancing the capability to manage and govern Kafka applications.
+2. Outcome (impact):
+Customers can now build, connect, and govern their Apache Kafka applications more effectively in the German region with fully managed, scalable, and secure tools.
+3. Where to use (use case):
+Ideal for organizations needing to manage streaming data workflows, ensuring data integrity and schema evolution across decoupled applications in compliance with German data sovereignty regulations.
+AWS Service: AWS Glue Schema Registry | Category: Analytics</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>Amazon MSK Connect</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>Streaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront announces dual-stack support for VPC origins</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/cloudfront-vpc-origin-dualstack/</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon CloudFront now supports IPv6 delivery to private VPC origins, allowing secure end-to-end IPv6 connectivity without exposing origins to the internet.
+2. Outcome (impact):  
+Customers can meet IPv6 requirements and regulatory compliance while maintaining the security of their private VPC resources.
+3. Where to use (use case):  
+Use dual-stack VPC origins for secure, private content delivery over IPv6, ideal for applications needing IPv6 support and stringent security.</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>PostgreSQL 19 RC1 is now available in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/postgresql-19-rc1-amazon-rds-database-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS now offers PostgreSQL 19 RC1 in its Database Preview Environment for evaluation, featuring stability improvements and new functionalities.
+2. Outcome (impact):
+   Users can test PostgreSQL 19's new features and improvements in a controlled environment, ensuring compatibility and stability before full release.
+3. Where to use (use case):
+   Ideal for developers and database administrators to test and validate applications against the upcoming PostgreSQL 19 release on AWS.</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>Amazon Redshift long-term system table retention with Amazon S3 Tables is now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/redshift-long-term-system-table-retention-expansion/</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Redshift now offers long-term retention of system table data in Amazon S3 Tables across additional regions, enhancing compliance and observability.
+2. Outcome (impact):
+   This feature allows customers to retain system table data beyond the 7-day limit, simplifying compliance, auditing, and performance monitoring while reducing ETL pipeline complexity.
+3. Where to use (use case):
+   Ideal for organizations needing extended retention of Redshift system table data for compliance, auditing, and cross-warehouse observability, particularly in regulated industries.</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>Amazon S3 Metadata now available in six additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-s3-metadata-six-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Metadata is now available in six new regions, enhancing data discovery and management capabilities.
+2. Outcome (impact):
+This expansion enables users to better curate, identify, and utilize their S3 data across more regions, improving analytics and real-time applications.
+3. Where to use (use case):
+Ideal for business analytics, real-time inference applications, and any use case requiring comprehensive and queryable metadata.</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>AWS Security Hub CSPM now supports the Cyber Risk Institute profile version 2.2</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/security-hub-cspm-cri-profile-v22/</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>1. Short Summary: AWS Security Hub CSPM now supports the Cyber Risk Institute profile version 2.2, providing automated security checks for financial services compliance.
+2. Outcome (impact): Organizations can now more easily align with financial sector cybersecurity and regulatory requirements, improving compliance and reducing manual effort.
+3. Where to use (use case): Ideal for financial institutions needing to comply with multiple regulations and cybersecurity frameworks simultaneously.</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus Collector now available in Asia Pacific (New Zealand) Region</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ams-prometheus-collector-apac-nz/</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Managed Service for Prometheus collector is now available in New Zealand, offering lower latency and local data residency for Prometheus-compatible monitoring.
+2. Outcome (impact):
+Customers in New Zealand can now run Prometheus-compatible monitoring workloads with reduced latency, simplified operations, and local data compliance.
+3. Where to use (use case):
+Ideal for monitoring container workloads in New Zealand, ensuring lower latency and local data storage for compliance.</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow now offers AI agent skills</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-mwaa-ai-agent-skills/</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Managed Workflows for Apache Airflow (MWAA) now integrates AI agent skills to simplify workflow authoring, debugging, testing, and environment upgrades using natural language.
+2. Outcome (impact):
+   Reduces manual effort in building and maintaining data pipelines, enhances productivity, and simplifies complex tasks through AI-assisted interactions.
+3. Where to use (use case):
+   Ideal for data engineers and developers who manage ETL pipelines and workflows in AWS, aiming to streamline workflow creation and maintenance.</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (MWAA)</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>Oracle Database@AWS supports aggregate and default routes for ODB peering</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/oracle-database-aws-aggregate-routes-odb/</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Oracle Database@AWS now supports aggregate and default routes for ODB peering, simplifying network operations for VPC and on-premises connectivity.
+2. Outcome (Impact):
+   Simplifies network management by allowing a single aggregate or default route to cover multiple networks, reducing the need for individual CIDR updates.
+3. Where to Use (Use Case):
+   Ideal for customers extending VPCs or on-premises networks to reach Oracle Database@AWS, especially when using AWS Transit Gateway for centralized network management.</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>Oracle Database@AWS</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>Launch AWS DevOps Agent to review findings and test results from AWS Resilience Hub</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-devops-agent-test-results-aws-resilience-hub/</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Resilience Hub now integrates with AWS DevOps Agent to review resilience test results and failure mode assessments, providing detailed analysis and mitigation plans.
+2. Outcome (impact):
+Enhanced ability to identify and resolve resilience issues in AWS workloads, leading to improved system reliability and quicker recovery actions.
+3. Where to use (use case):
+Platform engineering and site reliability teams can use this integration to assess and strengthen the resilience of their applications running on AWS.</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>AWS Resilience Hub</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics expands container registry support for private workflows</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-healthomics-expanded-container-registry-support/</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 21:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS HealthOmics now supports private workflows using container images from third-party registries like Seqera, NVIDIA NGC, and Google Artifact Registry, without manual migration to Amazon ECR.
+2. Outcome (impact):
+   This enhancement allows healthcare and life sciences customers to leverage their existing containerized tools directly in AWS HealthOmics, streamlining workflow management and reducing manual effort.
+3. Where to use (use case):
+   Ideal for bioinformatics workflows in healthcare and life sciences sectors, enabling the use of specialized tools and images from various registries without needing to manually manage image URIs.</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>AWS Lambda recursive loop detection now supports Amazon EventBridge Custom event buses</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/lambda-recursive-loops-eventbridge-custom</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda now detects and stops recursive loops between Lambda functions and Amazon EventBridge Custom event buses, preventing runaway usage and charges.
+2. Outcome (impact):
+   This feature helps protect users from unintended recursive loops caused by misconfigurations or code defects, reducing the risk of unexpected charges and system instability.
+3. Where to use (use case):
+   Ideal for automation workflows and scheduling recurring tasks using EventBridge Custom event buses to invoke Lambda functions.</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports the latest Cumulative Update for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-supports-latest-cumulative-update-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   Amazon RDS for SQL Server now supports the latest Cumulative Update (CU8) for Microsoft SQL Server, including improvements and fixes from KB5104822.
+2. Outcome (impact)
+   Users can benefit from the latest security patches, performance improvements, and bug fixes provided by Microsoft SQL Server 2025 CU8.
+3. Where to use (use case)
+   Ideal for businesses requiring up-to-date security and performance enhancements for their SQL Server databases hosted on AWS.</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -53086,7 +53899,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15 08:08:48</t>
+          <t>2026-10-16 08:01:50</t>
         </is>
       </c>
     </row>
@@ -53097,7 +53910,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -53107,7 +53920,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5994</v>
+        <v>8214</v>
       </c>
     </row>
     <row r="7">
@@ -53117,7 +53930,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1987</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="8">
@@ -53127,7 +53940,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000426</v>
+        <v>0.000583</v>
       </c>
     </row>
     <row r="9">
@@ -53137,7 +53950,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000564</v>
+        <v>0.000798</v>
       </c>
     </row>
     <row r="10">
@@ -53147,7 +53960,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00099</v>
+        <v>0.001381</v>
       </c>
     </row>
     <row r="11">
@@ -53157,7 +53970,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.087895</v>
+        <v>0.08927599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1440"/>
+  <dimension ref="A1:F1451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -53834,6 +53834,417 @@
       <c r="F1440" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch log centralization now available in AWS GovCloud and additional commercial Regions</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-cloudwatch-centralization-region-expansion</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 20:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now offers log centralization in AWS GovCloud and 13 additional commercial regions, enabling efficient log aggregation across accounts and regions.
+2. Outcome (impact):
+   Organizations can now centralize logs from multiple accounts and regions into a single destination account, improving monitoring efficiency and reducing the need for custom solutions.
+3. Where to use (use case):
+   Ideal for organizations requiring centralized log management across multiple AWS accounts and regions, including those in sensitive environments like AWS GovCloud and those needing regional compliance.</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>AWS Lambda durable functions are now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/durablefunctions-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 18:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Lambda durable functions are now available in AWS GovCloud (US) Regions, enabling reliable multi-step applications and AI workflows with checkpointing and recovery features.
+2. Outcome (impact):  
+Government customers and regulated industries can now build and manage complex, reliable processes while meeting compliance and security requirements.
+3. Where to use (use case):  
+Order workflows, user onboarding, and AI-assisted tasks in highly regulated environments.</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>Nemotron 3.5 Super VL model now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/nvidia-nemotron-3.5-super-vl-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 17:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+NVIDIA's Nemotron 3.5 Super VL model is now available on Amazon SageMaker JumpStart, enabling multimodal AI solutions.
+2. Outcome (impact):  
+AWS customers can now deploy advanced multimodal AI applications for document intelligence, GUI understanding, and more.
+3. Where to use (use case):  
+Ideal for document intelligence, GUI understanding, video question answering, and multimodal agentic applications.</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>Beam model by Reflection is now available on Amazon SageMaker JumpStart and AWS Trainium</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/reflection-beam-on-sagemaker-jumpstart-and-aws-trainium/</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Reflection's Beam model, an open-weight model, is now available on Amazon SageMaker JumpStart and optimized for AWS Trainium3, enabling advanced coding and automated workflows.
+2. Outcome (impact):  
+Customers can build and deploy advanced AI solutions with full control over their data and infrastructure, enhancing productivity and innovation while maintaining security and compliance.
+3. Where to use (use case):  
+- Resolving software issues  
+- Generating and reviewing code  
+- Automating routine operations  
+- Complex multi-step workflows  
+- Advanced math and science reasoning</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>AWS Transform announces Azure-to-AWS cloud-native code conversion</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-transform-azure-to-aws-code-conversion/</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 13:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now offers a tool to convert Azure-native.NET applications to AWS services, simplifying migration from Azure to AWS.
+2. Outcome (impact):  
+This feature accelerates the migration of Azure cloud-native applications to AWS, reducing manual effort and potential errors in code conversion.
+3. Where to use (use case):  
+Ideal for organizations looking to migrate their Azure-based .NET applications to AWS, such as serverless functions, storage, and databases.</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>Second-generation AWS Outposts racks now supported in the AWS Mexico (Central) Region</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-outposts-racks-mexico-central/</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded support for second-generation Outposts racks to the Mexico (Central) Region, enhancing hybrid cloud capabilities.
+2. Outcome (impact):
+This expansion allows organizations to deploy AWS services closer to their users in Mexico, improving latency and meeting data residency requirements.
+3. Where to use (use case):
+Ideal for businesses needing low-latency access to AWS services in Mexico, such as financial institutions, healthcare providers, and e-commerce companies.</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging adds registration improvements for faster, higher-quality submissions</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-end-user-messaging-adds-registration-improvements-for-faster-higher-quality-submissions</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS End User Messaging enhances registration processes with clearer guidance and examples to reduce submission errors and delays.
+2. Outcome (impact):
+   Faster and higher-quality messaging registrations, reducing delays and denials due to incomplete or incorrect submissions.
+3. Where to use (use case):
+   Ideal for businesses relying on SMS and RCS communications, ensuring compliance with regulatory requirements and improving message deliverability.</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging now supports Brand Profiles</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-end-user-messaging-now-supports-brand-profiles</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS End User Messaging introduces Brand Profiles to streamline brand information management across messaging channels.
+2. Outcome (impact):  
+   Reduces time and errors in brand registration processes, ensuring faster and consistent messaging across SMS, RCS, and WhatsApp.
+3. Where to use (use case):  
+   Ideal for businesses managing multiple brands or those needing to register their brand information across various messaging platforms.</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging now offers managed OTP verification end-to-end</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-end-user-messaging-adds-end-to-end-managed-OTP</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS End User Messaging now offers a fully managed OTP verification service, simplifying the setup and management of one-time passcodes for user verification.
+2. Outcome (impact):
+Developers can quickly implement a secure OTP verification process without managing phone numbers, carrier registrations, or code handling logic, reducing development time and operational overhead.
+3. Where to use (use case):
+Ideal for applications requiring user verification through OTP, such as account registration, password recovery, and secure access to services.</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging adds a guided wizard for RCS registration videos</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-end-user-messaging-adds-guided-wizard-rcs-registration-videos</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS End User Messaging introduces a guided wizard to simplify the RCS registration video capture process, ensuring compliance and reducing errors.
+2. Outcome (impact):
+   The wizard streamlines the RCS registration process by automating the sequence of messages, reducing errors, and accelerating the approval timeline for RCS agents.
+3. Where to use (use case):
+   This tool is ideal for businesses and developers involved in registering RCS agents, particularly in countries requiring video submissions like the United States.</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations is now available in Asia Pacific (Singapore)</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-transform-singapore</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 19:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform for migrations is now available in Singapore, offering data residency and lower latency for migrating workloads to the cloud.
+2. Outcome (impact):
+Enterprises can accelerate cloud migrations with enhanced data residency and reduced latency, leveraging AI-driven automation for a seamless migration experience.
+3. Where to use (use case):
+Ideal for enterprises looking to migrate on-premises workloads to AWS, including VMware, Hyper-V, KVM, bare metal, and hybrid environments.</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -53899,7 +54310,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16 08:01:50</t>
+          <t>2026-10-17 07:39:38</t>
         </is>
       </c>
     </row>
@@ -53910,7 +54321,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -53920,7 +54331,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8214</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="7">
@@ -53930,7 +54341,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2809</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="8">
@@ -53940,7 +54351,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000583</v>
+        <v>0.000287</v>
       </c>
     </row>
     <row r="9">
@@ -53950,7 +54361,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000798</v>
+        <v>0.000375</v>
       </c>
     </row>
     <row r="10">
@@ -53960,7 +54371,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001381</v>
+        <v>0.000661</v>
       </c>
     </row>
     <row r="11">
@@ -53970,7 +54381,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08927599999999999</v>
+        <v>0.089937</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1451"/>
+  <dimension ref="A1:F1452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -54243,6 +54243,43 @@
         </is>
       </c>
       <c r="F1451" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>Amazon Braket now in scope for FedRAMP Class C</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/braket-fedramp-class-c/</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Braket is now FedRAMP Class C authorized, enabling government customers to use it for quantum computing within a secure framework.
+2. Outcome (impact):
+Government entities and their service providers can now safely explore quantum computing with Amazon Braket, ensuring compliance with federal security standards.
+3. Where to use (use case):
+Ideal for government agencies and contractors needing to experiment with quantum computing while adhering to strict security regulations.</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>Amazon Braket</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
         <is>
           <t>AI/ML</t>
         </is>
@@ -54310,7 +54347,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17 07:39:38</t>
+          <t>2026-10-18 07:54:49</t>
         </is>
       </c>
     </row>
@@ -54321,7 +54358,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -54331,7 +54368,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4037</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7">
@@ -54341,7 +54378,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1319</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
@@ -54351,7 +54388,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000287</v>
+        <v>2.5e-05</v>
       </c>
     </row>
     <row r="9">
@@ -54361,7 +54398,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000375</v>
+        <v>3.2e-05</v>
       </c>
     </row>
     <row r="10">
@@ -54371,7 +54408,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000661</v>
+        <v>5.7e-05</v>
       </c>
     </row>
     <row r="11">
@@ -54381,7 +54418,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.089937</v>
+        <v>0.089994</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1452"/>
+  <dimension ref="A1:F1463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -54282,6 +54282,413 @@
       <c r="F1452" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer Global Resiliency now provides business users visibility into resiliency readiness across linked Regions</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-connect-global-resiliency-readiness-overview</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 21:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect introduces a Global Resiliency page for administrators to monitor and manage Region switch readiness across linked Regions.
+2. Outcome (impact):
+   Administrators can now easily verify their instance's resiliency posture, ensuring all critical resources are synchronized and ready for a Region switch, minimizing downtime and maintaining business continuity.
+3. Where to use (use case):
+   This feature is ideal for businesses utilizing Amazon Connect across multiple AWS Regions to ensure high availability and disaster recovery readiness.</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Omni is now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-cloudwatch-omni-8-regions/</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 19:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of Amazon CloudWatch Omni to eight new regions, enhancing observability across multiple cloud environments.
+2. Outcome (impact):
+This expansion allows users to monitor and troubleshoot applications more effectively across diverse cloud platforms, improving operational efficiency and reducing troubleshooting time.
+3. Where to use (use case):
+CloudWatch Omni is ideal for teams managing multi-cloud or hybrid environments, providing a unified observability experience for better application performance monitoring and root cause analysis.</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Omni</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>EC2 Image Builder now integrates with ASG for faster image builds</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/ec2-image-builder-asg-faster-builds/</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+EC2 Image Builder now integrates with Auto Scaling Groups (ASG) to speed up image builds by reusing existing instances, eliminating the need to launch new ones.
+2. Outcome (impact):
+Faster image build times and reduced costs by reusing running instances, leading to more efficient resource utilization.
+3. Where to use (use case):
+Ideal for environments requiring frequent image updates or builds, such as CI/CD pipelines, development environments, and testing setups.</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>EC2 Image Builder</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty adds optional threat detection rules for Runtime Monitoring</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/guardduty-runtime-optional-detection-rules/</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 16:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon GuardDuty now offers optional detection rules for Runtime Monitoring to enhance threat detection across EC2, EKS, and ECS environments.
+2. Outcome (impact):  
+   Improved detection of suspicious activities that may indicate security threats, allowing for quicker response and mitigation.
+3. Where to use (use case):  
+   Ideal for monitoring and securing Amazon EC2 instances, Amazon EKS, and Amazon ECS on both EC2 and AWS Fargate to identify potential security breaches.</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>Grok 4.7 is now available on Amazon Bedrock in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-bedrock-grok-4-7-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Bedrock now supports SpaceXAI Grok 4.7 in AWS GovCloud (US), enhancing coding, agentic tasks, and knowledge work.
+2. Outcome (impact):
+   Improved mixed-document handling, dependable coding with planning and error recovery, and enhanced browser-use agents for form fills and portal navigation.
+3. Where to use (use case):
+   Ideal for coding assistance, automated agentic tasks, and knowledge work in secure, compliance-focused environments.</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center now supports optimistic locking for users and groups in its identity store</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/iam-identity-store-optimistic-locking/</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS IAM Identity Center now supports optimistic locking for users and groups to prevent data conflicts during concurrent updates.
+2. Outcome (impact):  
+Optimistic locking ensures that update and delete operations on users and groups only succeed if the data hasn't changed since it was last read, reducing the risk of data overwrites.
+3. Where to use (use case):  
+Use this feature in environments with multiple administrators or automated workflows that manage user and group attributes to maintain data integrity.</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaConnect Router now supports high bitrate mode</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/mediaconnect-router-high-bitrate/</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental MediaConnect Router now offers high bitrate modes of 250 Mbps and 500 Mbps, enhancing content transport for professional broadcasters.
+2. Outcome (impact):
+This enhancement enables reliable and high-quality transport of high-value content, supporting industry-standard workflows and improving performance with reduced jitter.
+3. Where to use (use case):
+Ideal for professional broadcasters needing to transport high-value content in scenarios such as broadcast contribution, content distribution, and remote production.</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaConnect</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom now supports the latest Cumulative Update and GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-rds-custom-supports-latest-cumulative-update-gdr-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS Custom for SQL Server now supports the latest Microsoft SQL Server Cumulative Updates and GDR releases, including SQL Server 2019 and 2022.
+2. Outcome (impact):
+   Users can now apply the latest security and performance improvements directly to their RDS Custom SQL Server instances, ensuring they are up-to-date with the most recent Microsoft updates.
+3. Where to use (use case):
+   Ideal for enterprise environments requiring the latest SQL Server updates for compliance, security, and performance enhancements.</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server now supports snapshots on read replicas</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/rds-sqlserver-supports-snapshots-on-read-replicas</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 07:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for SQL Server now allows creating DB snapshots directly on read replicas, enhancing backup and disaster recovery flexibility.
+2. Outcome (impact):
+   This update enables faster Multi-AZ promotion and more predictable disaster recovery timelines by maintaining snapshot data on read replicas.
+3. Where to use (use case):
+   Ideal for organizations needing efficient backup strategies and reliable disaster recovery plans for SQL Server databases in AWS.</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>AWS Partner Central adds Solution Matching Engine performance insights</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/solution-matching-engine-performance</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 03:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central now offers enhanced visibility into the Solution Matching Engine's impact on partners' co-sell pipeline through detailed performance insights.
+2. Outcome (impact):
+Partners can better assess their visibility and improve their AWS Marketplace listings and opportunity information, leading to more effective engagement with AWS sellers.
+3. Where to use (use case):
+This feature is ideal for AWS Partners aiming to optimize their co-sell opportunities and enhance their market presence by understanding and leveraging SME performance data.</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless now supports IPv6 and dual-stack connectivity</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-emr-serverless/</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 19:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR Serverless now supports IPv6 and dual-stack connectivity, allowing for flexible and compliant networking.
+2. Outcome (impact):
+This update provides greater flexibility in connecting applications to data stores and services, mitigates IPv4 address exhaustion, and meets compliance requirements for IPv6 adoption.
+3. Where to use (use case):
+Ideal for running Apache Spark and Apache Hive jobs in environments needing IPv6 support, such as those facing IPv4 address constraints or compliance mandates.</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -54347,7 +54754,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18 07:54:49</t>
+          <t>2026-10-20 08:21:58</t>
         </is>
       </c>
     </row>
@@ -54358,7 +54765,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -54368,7 +54775,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="7">
@@ -54378,7 +54785,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="8">
@@ -54388,7 +54795,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5e-05</v>
+        <v>0.000264</v>
       </c>
     </row>
     <row r="9">
@@ -54398,7 +54805,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2e-05</v>
+        <v>0.000387</v>
       </c>
     </row>
     <row r="10">
@@ -54408,7 +54815,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7e-05</v>
+        <v>0.00065</v>
       </c>
     </row>
     <row r="11">
@@ -54418,7 +54825,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.089994</v>
+        <v>0.090644</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1463"/>
+  <dimension ref="A1:F1477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -54689,6 +54689,524 @@
       <c r="F1463" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>Announcing Amazon ECS Gateway, a managed ingress solution for your ECS services</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/announcing-amazon-ecs-gateway/</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 23:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces Amazon ECS Gateway, a managed ingress solution for ECS services, simplifying ALB provisioning and management for containerized applications.
+2. Outcome (Impact):
+   Simplifies ingress networking, centralizes governance, reduces networking expertise requirements, optimizes infrastructure costs, and enhances traffic monitoring.
+3. Where to Use (Use Case):
+   Ideal for organizations looking to standardize and manage ingress traffic for multiple ECS services with minimal networking overhead.</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>Amazon ECS Gateway</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB global tables now support disassociating replicas</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/dynamodb-global-tables-disassociate/</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DynamoDB global tables now allow disassociation of replicas without deleting tables or data, enabling continued use as single-region tables.
+2. Outcome (impact):
+   This feature provides flexibility in managing multi-region tables, allowing accounts to leave shared tables and use them independently, or stop replication for local workloads without data loss.
+3. Where to use (use case):
+   Ideal for scenarios requiring independent use of tables in different regions, such as local data processing, validation, or audit without maintaining a separate table.</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>DynamoDB</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>Polly Generative engine upgraded with more natural speech, 14 new voices, and 2 new languages</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/polly-generative/</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 15:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Polly's Generative engine now offers more natural speech, 14 new voices, and support for Hindi and Finnish.
+2. Outcome (impact):
+   Enhanced voice quality and expanded language support improve user experience for applications like contact centers, chatbots, and media.
+3. Where to use (use case):
+   Ideal for contact centers, chatbots, e-learning, media, entertainment, and accessibility applications.</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>Amazon Polly</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>AWS announces TorchNeuron: Native PyTorch Support for AWS Trainium (Public Beta)</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-announce-native-pytorch-support-trainium</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched TorchNeuron, an open-source PyTorch backend for AWS Trainium, enabling native PyTorch support on Trainium chips.
+2. Outcome (impact):  
+TorchNeuron allows AI scientists and researchers to build and experiment with PyTorch models directly on Trainium hardware, enhancing performance and cost efficiency for deep learning tasks.
+3. Where to use (use case):  
+Ideal for deep learning model training and inference on AWS Trainium instances, particularly for AI research and development.</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>AWS Trainium</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>Structured outputs for Claude models available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/claude-structured-outputs-bedrock/</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now supports structured outputs for Anthropic's Claude models, enabling schema-compliant JSON responses without custom parsing.
+2. Outcome (Impact):
+This update enhances automation and reliability for tasks requiring structured data, such as financial report extraction, clinical note parsing, and contract analysis.
+3. Where to Use (Use Case):
+Ideal for industries needing consistent, validated data extraction and analysis, such as finance, healthcare, legal, and e-commerce.</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms now supports Databricks as a data source</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-clean-rooms-supports-databricks</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 12:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Clean Rooms now supports Databricks as a data source, enabling secure data analysis without data movement or exposure.
+2. Outcome (impact):
+Eliminates the need for data export or replication to Amazon S3, reducing pipeline complexity and data governance challenges.
+3. Where to use (use case):
+Retailers collaborating with media partners to measure campaign effectiveness using customer data stored in Databricks.</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center simplifies identity source changes from Active Directory</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/iam-identity-center-chg-id-src-from-ad/</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS IAM Identity Center now retains user identities and assignments when switching from Active Directory to external IdPs, eliminating the need for recreation.
+2. Outcome (impact):
+   Simplifies migration to external identity providers by preserving user identities, groups, and permissions, ensuring uninterrupted access and policy continuity.
+3. Where to use (use case):
+   Ideal for organizations transitioning from on-premises Active Directory to cloud-based identity management solutions like Okta or Microsoft Entra ID.</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>AWS Partner Central launches Program Navigator, Case Study Generator, and streamlined specialization review</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/partner-central-program-navigator/</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Partner Central introduces Program Navigator for streamlined AWS Specialization applications and a Case Study Generator with AI assistance.
+2. Outcome (impact):
+   Partners can efficiently discover, apply for, and track AWS Specializations, and create case studies faster with improved review processes.
+3. Where to use (use case):
+   Ideal for AWS Partners seeking to enhance their AWS Specialization applications and create compelling customer success stories.</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Guardrails now supports Standard tier for contextual grounding checks</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/bedrock-guardrails-grounding-standard/</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Bedrock Guardrails introduces a Standard tier for contextual grounding checks, enhancing detection and filtering of hallucinations in conversational AI applications.
+2. Outcome (Impact):
+   The new Standard tier improves the robustness of contextual grounding checks, making it suitable for conversational content and reasoning tasks, thus reducing inaccuracies and enhancing user experience.
+3. Where to Use (Use Case):
+   Ideal for conversational AI applications, customer support chatbots, and any generative AI systems requiring reliable and contextually accurate responses.</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Guardrails</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Advanced Prompt Optimization now supports prompt shortening</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/bedrock-prompt-optimization-shortening/</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock's Advanced Prompt Optimization now includes prompt shortening, reducing prompt length while maintaining or improving evaluation scores.
+2. Outcome (impact):
+Reduces input token costs and improves efficiency in latency-sensitive applications by shortening prompts without compromising quality.
+3. Where to use (use case):
+Ideal for applications requiring quick response times and cost-effective token usage, such as chatbots, real-time analytics, and large-scale AI model deployments.</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations expands support for existing landing zones</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-transform-migrations-landing-zones/</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now supports more existing AWS environments and IaC-only mode for migration landing zones.
+2. Outcome (impact):  
+Enables faster migrations by leveraging existing AWS environments and infrastructure as code, reducing setup time and complexity.
+3. Where to use (use case):  
+Ideal for organizations migrating to AWS with existing AWS Control Tower or AWS Organizations setups, and those preferring IaC management.</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Alarms now supports tags in alarm actions payload</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-cloudwatch-tags-on-alarm-actions-payload</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now allows alarm tags to be included in action payloads, enabling better notification routing and filtering by tag.
+2. Outcome (impact):
+   This feature simplifies alarm management by reducing the need for additional lookups to correlate tags with alarm events, enhancing efficiency and accuracy in notification pipelines.
+3. Where to use (use case):
+   Ideal for teams managing multiple alarms through shared notification channels (e.g., SNS topics, Lambda functions) who need to quickly identify the alarm's context (e.g., owning team, environment) directly from the notification.</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache Serverless for Valkey now supports online migration with zero downtime</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-elasticache-serverless-valkey-online-migration/</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon ElastiCache Serverless for Valkey now supports zero-downtime online migration from self-managed Valkey and Redis on EC2.
+2. Outcome (impact):  
+Ensures continuous application availability with no client errors during migration, eliminating the need for third-party replication tools.
+3. Where to use (use case):  
+Ideal for migrating existing Valkey and Redis databases to ElastiCache Serverless with minimal disruption, suitable for production environments requiring high availability.</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports configurable time-to-live for long-term memory</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/agentcore-memory-long-term-memory-ttl</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now allows setting a time-to-live (TTL) for long-term memory records, enabling automatic deletion after a specified retention period.
+2. Outcome (impact):
+This feature helps meet data-retention requirements, control storage growth, and ensure that outdated insights are removed from memory over time.
+3. Where to use (use case):
+Ideal for applications requiring compliance with data retention policies, managing storage costs, and maintaining up-to-date insights in conversational AI systems.</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -54754,7 +55272,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 08:21:58</t>
+          <t>2026-10-21 08:25:42</t>
         </is>
       </c>
     </row>
@@ -54765,7 +55283,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -54775,7 +55293,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3713</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="7">
@@ -54785,7 +55303,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1362</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="8">
@@ -54795,7 +55313,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000264</v>
+        <v>0.000383</v>
       </c>
     </row>
     <row r="9">
@@ -54805,7 +55323,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000387</v>
+        <v>0.000485</v>
       </c>
     </row>
     <row r="10">
@@ -54815,7 +55333,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00065</v>
+        <v>0.000868</v>
       </c>
     </row>
     <row r="11">
@@ -54825,7 +55343,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.090644</v>
+        <v>0.091512</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1477"/>
+  <dimension ref="A1:F1487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -55205,6 +55205,376 @@
         </is>
       </c>
       <c r="F1477" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>AWS Transform adds storage migration assessments for Amazon S3, EBS, EFS, and FSx</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/transform-assess-s3-ebs-efs-fsx/</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 19:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now offers automated storage migration assessments for on-premises storage to AWS services, simplifying the migration process and cost projection.
+2. Outcome (impact):  
+Reduces manual effort in analyzing storage migration needs, provides accurate mappings and cost projections, and streamlines the migration planning process.
+3. Where to use (use case):  
+Ideal for organizations planning to migrate their on-premises storage infrastructure to AWS, helping them choose the best-fit AWS storage services and optimize costs.</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect announces 100G expansion in Manchester, England</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-direct-connect-100g-manchester/</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 17:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Direct Connect has expanded its 100 Gbps dedicated connections with MACsec encryption in Manchester, England, enabling private network access to all public and GovCloud regions.
+2. Outcome (impact):  
+This expansion enhances network performance and security for businesses in the UK, offering faster and more reliable connections to AWS services.
+3. Where to use (use case):  
+Ideal for enterprises needing high-speed, secure, and consistent connectivity to AWS services for applications requiring low latency and high throughput.</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>Amazon Aurora and Amazon RDS now support On-Demand Capacity Reservations</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-aurora-rds-on-demand-capacity-reservations/</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Aurora and RDS now offer On-Demand Capacity Reservations to ensure DB instance operations don't fail due to insufficient capacity.
+2. Outcome (impact):  
+Ensures availability of compute capacity for critical business events, reducing the risk of operation failures during peak times.
+3. Where to use (use case):  
+Ideal for business-critical events like migrations, product launches, seasonal peaks, and disaster recovery.</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>Amazon Cognito extends multi-Region replication to AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/cognito-multi-region-us-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Cognito's multi-Region replication now supports AWS GovCloud (US) Regions, enhancing resilience and data availability.
+2. Outcome (impact):
+This extension allows organizations to meet compliance and resilience requirements by synchronizing identity data across regions, ensuring business continuity.
+3. Where to use (use case):
+Ideal for government and regulated industries needing high data security and compliance, ensuring authentication availability during regional disruptions.</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>AWS Neuron 2.33 adds native PyTorch support, Neuron Observer, and other new features</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-announce-neuron-2-33-0</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Neuron 2.33 introduces TorchNeuron for native PyTorch support on AWS Trainium and Neuron Observer for quick health issue detection.
+2. Outcome (impact):
+   Enhanced performance and debugging capabilities for PyTorch models on AWS Trainium, facilitating faster model training and easier issue resolution.
+3. Where to use (use case):
+   Ideal for deep learning researchers and developers working with PyTorch models on AWS Trainium instances for tasks like model training, debugging, and optimization.</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>AWS Trainium</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches two new layouts for agent workspace</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/connect-customer-new-layouts-agent-workspace</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 13:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer introduces two new agent workspace layouts to enhance screen space and agent efficiency.
+2. Outcome (impact):
+   Administrators can now select the optimal layout for their teams, improving agent productivity and satisfaction by tailoring the workspace to specific workflows and contact channels.
+3. Where to use (use case):
+   Suitable for contact centers where agents handle multiple communication channels and require a customized workspace to streamline their tasks.</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>Amazon S3 server access log delivery to Amazon CloudWatch Logs now available in five additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-s3-server-access-logs-cloudwatch-logs-regions/</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 server access logs can now be delivered to Amazon CloudWatch Logs in five additional AWS Regions, enhancing monitoring and analysis capabilities.
+2. Outcome (impact):
+This update provides greater flexibility and real-time monitoring of S3 access logs, enabling better security, performance tuning, and incident investigation.
+3. Where to use (use case):
+Ideal for organizations needing real-time monitoring, alerting, and correlation of S3 access data with other operational metrics to enhance security and operational insights.</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI now supports custom sequence lengths for serverless model customization jobs</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/sagemaker-custom-sequence-lengths/</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker AI now allows users to customize sequence lengths for serverless model fine-tuning jobs, enhancing flexibility and performance.
+2. Outcome (impact):
+Users can now achieve better model performance by adjusting sequence lengths to better match their specific use cases, leading to more accurate and efficient model training.
+3. Where to use (use case):
+This feature is ideal for users working with varying lengths of text data, such as short question-answer pairs or extensive documents, in applications like customer support, document analysis, and more.</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall now supports Route 53 Resolved IP Validation</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/network-firewall-route-53-ip-validation/</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Network Firewall now validates domain-based IP addresses via Route 53, enhancing security for protocols like SFTP and SSH.
+2. Outcome (impact):
+   This feature closes security gaps, prevents SNI spoofing, and allows consistent domain-based security policies across all traffic types.
+3. Where to use (use case):
+   Ideal for organizations needing robust security policies for various protocols, ensuring only legitimate domain resolutions are allowed.</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces simplifies secure AI agent access to enterprise cloud desktops with less infrastructure to operate and manage</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/workspaces-ai-agents-oauth-connection-management</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon WorkSpaces for AI agents simplifies secure access to cloud desktops with enhanced authentication and session management.
+2. Outcome (impact):  
+   Reduces operational complexity and infrastructure management for deploying AI agents on cloud desktops, enabling easier integration and observability.
+3. Where to use (use case):  
+   Ideal for enterprises deploying AI agents that require secure, governed access to cloud desktops for tasks such as data analysis, application testing, and automated workflows.</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
         <is>
           <t>AI/ML</t>
         </is>
@@ -55272,7 +55642,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21 08:25:42</t>
+          <t>2026-10-22 08:27:58</t>
         </is>
       </c>
     </row>
@@ -55283,7 +55653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -55293,7 +55663,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5400</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="7">
@@ -55303,7 +55673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1706</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="8">
@@ -55313,7 +55683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000383</v>
+        <v>0.000267</v>
       </c>
     </row>
     <row r="9">
@@ -55323,7 +55693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000485</v>
+        <v>0.000342</v>
       </c>
     </row>
     <row r="10">
@@ -55333,7 +55703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000868</v>
+        <v>0.0006089999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -55343,7 +55713,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.091512</v>
+        <v>0.09212099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1487"/>
+  <dimension ref="A1:F1500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -55577,6 +55577,488 @@
       <c r="F1487" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports customizing the Customer Profiles app on the agent workspace</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/connect-customer-customize-cp</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 21:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect now allows admins to customize customer data views for agents, enhancing interaction efficiency.
+2. Outcome (impact):
+Improves agent productivity by providing relevant customer data tailored to specific roles, leading to faster and more informed customer service.
+3. Where to use (use case):
+Ideal for customer service scenarios where different agents handle various types of customer interactions, such as support, loyalty, and claims.</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>AWS Continuum for code vulnerabilities is now generally available</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-continuum-for-code-vulnerabilities-is-now-generally-available</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Continuum for code vulnerabilities automates the discovery, validation, prioritization, and remediation of code vulnerabilities at machine speed.
+2. Outcome (impact):  
+Enhances security posture by identifying and mitigating real business risks, reduces manual effort, and accelerates the remediation process.
+3. Where to use (use case):  
+Ideal for development teams and security operations within organizations that need to manage and mitigate code vulnerabilities efficiently.</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>AWS Continuum</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Serverless now supports a 5-second default refresh interval</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-opensearch-serverless-supports-5-second-refresh-interval/</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 18:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Serverless now defaults to a 5-second refresh interval, enhancing search and vector data availability.
+2. Outcome (impact):
+Newly ingested data becomes searchable faster, improving real-time data retrieval for applications.
+3. Where to use (use case):
+Ideal for applications requiring near real-time data access, such as full-text search, RAG, semantic search, and recommendation systems.</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Serverless</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation now simplifies stack update rollback operations</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-cloudformation-cdk/</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CloudFormation now simplifies stack update rollbacks with a force rollback option, enabling a single operation to revert to a deployable state.
+2. Outcome (impact):
+Efficiency in managing stack updates is improved, reducing manual intervention and time needed to resolve rollback issues.
+3. Where to use (use case):
+Ideal for managing infrastructure as code deployments where quick recovery from failed updates is crucial.</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>CloudFormation</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI announces training session APIs for serverless model customization</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/training-session-apis-on-sagemaker-ai</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker AI introduces training session APIs for serverless model customization, enabling full control over post-training algorithms without managing GPU infrastructure.
+2. Outcome (impact):  
+Customers can now implement custom training loops for supervised fine-tuning, reinforcement learning, and other techniques, with SageMaker handling infrastructure and execution.
+3. Where to use (use case):  
+Ideal for data scientists and ML engineers who need to fine-tune models, implement reinforcement learning, or develop custom training procedures without dealing with underlying infrastructure.</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect announces 100G expansion in Bangalore, India</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-direct-connect-100g-bangalore/</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Direct Connect has expanded its 100 Gbps dedicated connections in Bangalore, India, enabling private network access to all public and GovCloud Regions.
+2. Outcome (Impact):  
+This expansion allows businesses in India to achieve more consistent and reliable network performance by connecting directly to AWS services.
+3. Where to Use (Use Case):  
+Ideal for enterprises requiring high-throughput and low-latency network connections for applications such as data warehousing, content delivery, and real-time analytics.</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Interconnect - last mile preview with Megaport</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-announces-AWS-interconnect-last-mile-megaport-preview/</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched AWS Interconnect - last mile preview with Megaport, a managed service simplifying private, high-speed connections to AWS with automated network setup.
+2. Outcome (impact):
+This service reduces the complexity and friction of network setup, allowing businesses to quickly and efficiently connect their on-premises infrastructure to AWS.
+3. Where to use (use case):
+Ideal for businesses needing to connect branch offices, data centers, and remote locations to AWS with minimal setup effort, ensuring high availability and reliability.</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>AWS Interconnect - last mile</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI now supports serverless model customization for Muse Glimmer, Qwen 3.8 and Ministral 3 models</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-sagemaker-muse-qwen-ministral/</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker now supports serverless model customization for Muse Glimmer, Qwen 3.8, and Ministral 3 models, enabling domain-specific adaptations using various fine-tuning techniques.
+2. Outcome (impact):
+This update allows users to tailor large language models to their specific needs, improving performance on domain-specific tasks while reducing costs and latency. It simplifies model customization by handling infrastructure and training orchestration.
+3. Where to use (use case):
+Customizing large language models for specific industries or internal workflows, such as legal, medical, or financial sectors, to improve accuracy and alignment with organizational standards.</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>AgentCore Gateway now supports Bedrock InvokeModel APIs and model fallback</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/agentcore-gateway-invokemodel-fallback/</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Gateway now supports InvokeModel APIs and model fallback, enabling seamless integration with multiple model providers and automatic fallback routing.
+2. Outcome (impact):
+This update allows developers to manage multiple model providers through a single endpoint, ensuring high availability and reducing the need for custom retry logic, thereby improving application resilience and developer efficiency.
+3. Where to use (use case):
+Ideal for applications requiring robust, multi-provider model integration and high availability, such as conversational AI systems, recommendation engines, and any service needing dynamic model selection.</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Gateway</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>AWS Lambda MicroVMs is now available in 4 additional AWS regions</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/lambda-microvms-4-additional-regions</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 07:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda MicroVMs are now available in 4 new regions, enhancing global accessibility and performance for developers.
+2. Outcome (impact):
+   Developers can now deploy isolated, stateful compute environments closer to end-users, improving latency and meeting data residency requirements.
+3. Where to use (use case):
+   Ideal for AI coding assistants, interactive development environments, and vulnerability scanners requiring secure, isolated execution.</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>AWS Lambda MicroVMs</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>Amazon Quick Now Available in the AWS Singapore Region</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/amazon-quick-now-available-in-the-aws-singapore-region/</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick is now available in the AWS Asia Pacific (Singapore) region, enabling local data sovereignty and access to AI-powered features.
+2. Outcome (impact):
+Customers in Singapore can now leverage Amazon Quick's capabilities, including AI-powered chat, research, Spaces, and QuickSight dashboards, with data stored locally.
+3. Where to use (use case):
+Businesses in Singapore needing AI-driven insights and actions within a trusted local data environment.</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>AWS Service Reference Information now supports global condition keys, service names, and data plane classification</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-service-reference-information-global-condition-keys-service-names-data-plane/</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS enhances service reference data with global condition keys, service names, and data plane classifications to streamline IAM policy management.
+2. Outcome (Impact):
+   This update simplifies automating IAM policy management, ensuring policies stay current with AWS service updates, reducing manual effort, and minimizing errors.
+3. Where to Use (Use Case):
+   Ideal for organizations managing complex IAM policies across multiple services, aiming to automate policy updates and maintain alignment with AWS service changes.</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>AWS Identity and Access Management (IAM)</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>AWS Transform now builds new networks and modernizes security groups</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/10/aws-transform-new-networks/</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Transform now offers three methods to migrate, build, or modernize your network on AWS, ensuring a secure and scalable foundation.
+2. Outcome (impact):
+   Users can choose to migrate existing networks, build new ones from scratch, or convert on-premises rules into optimized security groups, leading to more efficient and secure AWS deployments.
+3. Where to use (use case):
+   Ideal for organizations looking to migrate to AWS, whether they need to maintain legacy rules or start fresh with AWS best practices.</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -55642,7 +56124,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22 08:27:58</t>
+          <t>2026-10-23 08:24:10</t>
         </is>
       </c>
     </row>
@@ -55653,7 +56135,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -55663,7 +56145,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3767</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="7">
@@ -55673,7 +56155,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1204</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="8">
@@ -55683,7 +56165,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000267</v>
+        <v>0.000329</v>
       </c>
     </row>
     <row r="9">
@@ -55693,7 +56175,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000342</v>
+        <v>0.000456</v>
       </c>
     </row>
     <row r="10">
@@ -55703,7 +56185,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0006089999999999999</v>
+        <v>0.000785</v>
       </c>
     </row>
     <row r="11">
@@ -55713,7 +56195,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09212099999999999</v>
+        <v>0.092906</v>
       </c>
     </row>
   </sheetData>
